--- a/РАБОЧИЙ СТОЛ/расчет Останкино КИ/дв 06,07,26 днрсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет Останкино КИ/дв 06,07,26 днрсч ост ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBEF4EF-42C8-4D4A-A97C-84ED49F6B890}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3B3D58-CCF5-4E35-9F60-EBA0B94E1849}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AB$108</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="149">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -467,6 +467,18 @@
   <si>
     <t>БОНУС_6954 СОЧНЫЕ Папа может сос п/о мгс 1.5*4_Х5  ОСТАНКИНО</t>
   </si>
+  <si>
+    <t>07,07,26 +600шт в заказ (просьба Босых под сети)</t>
+  </si>
+  <si>
+    <t>07,07,26 +400шт в заказ (просьба Босых под сети)</t>
+  </si>
+  <si>
+    <t>07,07,26 +600шт в заказ (просьба Босых под сети - просил 700) / нужно увеличить продажи</t>
+  </si>
+  <si>
+    <t>ВНИМАНИЕ / 7080</t>
+  </si>
 </sst>
 </file>
 
@@ -475,7 +487,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,6 +525,13 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -595,7 +614,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -614,6 +633,8 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -917,8 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AV498"/>
+  <dimension ref="A1:AT498"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -937,10 +957,10 @@
     <col min="21" max="26" width="6" customWidth="1"/>
     <col min="27" max="27" width="36.140625" customWidth="1"/>
     <col min="28" max="28" width="7" customWidth="1"/>
-    <col min="29" max="48" width="3" customWidth="1"/>
+    <col min="29" max="46" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -987,10 +1007,8 @@
       <c r="AR1" s="8"/>
       <c r="AS1" s="8"/>
       <c r="AT1" s="8"/>
-      <c r="AU1" s="8"/>
-      <c r="AV1" s="8"/>
-    </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1037,10 +1055,8 @@
       <c r="AR2" s="8"/>
       <c r="AS2" s="8"/>
       <c r="AT2" s="8"/>
-      <c r="AU2" s="8"/>
-      <c r="AV2" s="8"/>
-    </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1143,10 +1159,8 @@
       <c r="AR3" s="8"/>
       <c r="AS3" s="8"/>
       <c r="AT3" s="8"/>
-      <c r="AU3" s="8"/>
-      <c r="AV3" s="8"/>
-    </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1211,10 +1225,8 @@
       <c r="AR4" s="8"/>
       <c r="AS4" s="8"/>
       <c r="AT4" s="8"/>
-      <c r="AU4" s="8"/>
-      <c r="AV4" s="8"/>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1261,7 +1273,7 @@
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
-        <v>16516.374400000001</v>
+        <v>18116.374400000004</v>
       </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
@@ -1292,7 +1304,7 @@
       <c r="AA5" s="8"/>
       <c r="AB5" s="3">
         <f>SUM(AB6:AB498)</f>
-        <v>7529.8904000000011</v>
+        <v>8063.8904000000011</v>
       </c>
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
@@ -1312,10 +1324,8 @@
       <c r="AR5" s="8"/>
       <c r="AS5" s="8"/>
       <c r="AT5" s="8"/>
-      <c r="AU5" s="8"/>
-      <c r="AV5" s="8"/>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>30</v>
       </c>
@@ -1419,10 +1429,8 @@
       <c r="AR6" s="8"/>
       <c r="AS6" s="8"/>
       <c r="AT6" s="8"/>
-      <c r="AU6" s="8"/>
-      <c r="AV6" s="8"/>
-    </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>32</v>
       </c>
@@ -1521,10 +1529,8 @@
       <c r="AR7" s="8"/>
       <c r="AS7" s="8"/>
       <c r="AT7" s="8"/>
-      <c r="AU7" s="8"/>
-      <c r="AV7" s="8"/>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>34</v>
       </c>
@@ -1628,10 +1634,8 @@
       <c r="AR8" s="8"/>
       <c r="AS8" s="8"/>
       <c r="AT8" s="8"/>
-      <c r="AU8" s="8"/>
-      <c r="AV8" s="8"/>
-    </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>36</v>
       </c>
@@ -1685,7 +1689,7 @@
         <v>188.56040000000002</v>
       </c>
       <c r="R9" s="4">
-        <f t="shared" ref="R7:R26" si="8">14*Q9-P9-O9-F9</f>
+        <f t="shared" ref="R9:R25" si="8">14*Q9-P9-O9-F9</f>
         <v>567.22860000000014</v>
       </c>
       <c r="S9" s="8">
@@ -1737,10 +1741,8 @@
       <c r="AR9" s="8"/>
       <c r="AS9" s="8"/>
       <c r="AT9" s="8"/>
-      <c r="AU9" s="8"/>
-      <c r="AV9" s="8"/>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
@@ -1841,10 +1843,8 @@
       <c r="AR10" s="8"/>
       <c r="AS10" s="8"/>
       <c r="AT10" s="8"/>
-      <c r="AU10" s="8"/>
-      <c r="AV10" s="8"/>
-    </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>39</v>
       </c>
@@ -1947,10 +1947,8 @@
       <c r="AR11" s="8"/>
       <c r="AS11" s="8"/>
       <c r="AT11" s="8"/>
-      <c r="AU11" s="8"/>
-      <c r="AV11" s="8"/>
-    </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>40</v>
       </c>
@@ -2056,10 +2054,8 @@
       <c r="AR12" s="8"/>
       <c r="AS12" s="8"/>
       <c r="AT12" s="8"/>
-      <c r="AU12" s="8"/>
-      <c r="AV12" s="8"/>
-    </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>41</v>
       </c>
@@ -2158,10 +2154,8 @@
       <c r="AR13" s="8"/>
       <c r="AS13" s="8"/>
       <c r="AT13" s="8"/>
-      <c r="AU13" s="8"/>
-      <c r="AV13" s="8"/>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>42</v>
       </c>
@@ -2267,10 +2261,8 @@
       <c r="AR14" s="8"/>
       <c r="AS14" s="8"/>
       <c r="AT14" s="8"/>
-      <c r="AU14" s="8"/>
-      <c r="AV14" s="8"/>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>43</v>
       </c>
@@ -2373,10 +2365,8 @@
       <c r="AR15" s="8"/>
       <c r="AS15" s="8"/>
       <c r="AT15" s="8"/>
-      <c r="AU15" s="8"/>
-      <c r="AV15" s="8"/>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>44</v>
       </c>
@@ -2425,10 +2415,12 @@
         <f t="shared" si="4"/>
         <v>117.8</v>
       </c>
-      <c r="R16" s="4"/>
+      <c r="R16" s="18">
+        <v>600</v>
+      </c>
       <c r="S16" s="8">
         <f t="shared" si="5"/>
-        <v>15.704584040747029</v>
+        <v>20.797962648556876</v>
       </c>
       <c r="T16" s="8">
         <f t="shared" si="6"/>
@@ -2452,10 +2444,12 @@
       <c r="Z16" s="8">
         <v>74.8</v>
       </c>
-      <c r="AA16" s="8"/>
+      <c r="AA16" s="16" t="s">
+        <v>145</v>
+      </c>
       <c r="AB16" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AC16" s="8"/>
       <c r="AD16" s="8"/>
@@ -2475,10 +2469,8 @@
       <c r="AR16" s="8"/>
       <c r="AS16" s="8"/>
       <c r="AT16" s="8"/>
-      <c r="AU16" s="8"/>
-      <c r="AV16" s="8"/>
-    </row>
-    <row r="17" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>46</v>
       </c>
@@ -2584,10 +2576,8 @@
       <c r="AR17" s="8"/>
       <c r="AS17" s="8"/>
       <c r="AT17" s="8"/>
-      <c r="AU17" s="8"/>
-      <c r="AV17" s="8"/>
-    </row>
-    <row r="18" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>47</v>
       </c>
@@ -2689,10 +2679,8 @@
       <c r="AR18" s="8"/>
       <c r="AS18" s="8"/>
       <c r="AT18" s="8"/>
-      <c r="AU18" s="8"/>
-      <c r="AV18" s="8"/>
-    </row>
-    <row r="19" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -2796,10 +2784,8 @@
       <c r="AR19" s="8"/>
       <c r="AS19" s="8"/>
       <c r="AT19" s="8"/>
-      <c r="AU19" s="8"/>
-      <c r="AV19" s="8"/>
-    </row>
-    <row r="20" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>49</v>
       </c>
@@ -2903,10 +2889,8 @@
       <c r="AR20" s="8"/>
       <c r="AS20" s="8"/>
       <c r="AT20" s="8"/>
-      <c r="AU20" s="8"/>
-      <c r="AV20" s="8"/>
-    </row>
-    <row r="21" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>50</v>
       </c>
@@ -3008,10 +2992,8 @@
       <c r="AR21" s="8"/>
       <c r="AS21" s="8"/>
       <c r="AT21" s="8"/>
-      <c r="AU21" s="8"/>
-      <c r="AV21" s="8"/>
-    </row>
-    <row r="22" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>51</v>
       </c>
@@ -3033,7 +3015,9 @@
       <c r="G22" s="6">
         <v>1</v>
       </c>
-      <c r="H22" s="8"/>
+      <c r="H22" s="8">
+        <v>40</v>
+      </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8">
@@ -3109,10 +3093,8 @@
       <c r="AR22" s="8"/>
       <c r="AS22" s="8"/>
       <c r="AT22" s="8"/>
-      <c r="AU22" s="8"/>
-      <c r="AV22" s="8"/>
-    </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>52</v>
       </c>
@@ -3213,10 +3195,8 @@
       <c r="AR23" s="8"/>
       <c r="AS23" s="8"/>
       <c r="AT23" s="8"/>
-      <c r="AU23" s="8"/>
-      <c r="AV23" s="8"/>
-    </row>
-    <row r="24" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>53</v>
       </c>
@@ -3322,10 +3302,8 @@
       <c r="AR24" s="8"/>
       <c r="AS24" s="8"/>
       <c r="AT24" s="8"/>
-      <c r="AU24" s="8"/>
-      <c r="AV24" s="8"/>
-    </row>
-    <row r="25" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>54</v>
       </c>
@@ -3431,10 +3409,8 @@
       <c r="AR25" s="8"/>
       <c r="AS25" s="8"/>
       <c r="AT25" s="8"/>
-      <c r="AU25" s="8"/>
-      <c r="AV25" s="8"/>
-    </row>
-    <row r="26" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>55</v>
       </c>
@@ -3533,10 +3509,8 @@
       <c r="AR26" s="8"/>
       <c r="AS26" s="8"/>
       <c r="AT26" s="8"/>
-      <c r="AU26" s="8"/>
-      <c r="AV26" s="8"/>
-    </row>
-    <row r="27" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>56</v>
       </c>
@@ -3626,10 +3600,8 @@
       <c r="AR27" s="8"/>
       <c r="AS27" s="8"/>
       <c r="AT27" s="8"/>
-      <c r="AU27" s="8"/>
-      <c r="AV27" s="8"/>
-    </row>
-    <row r="28" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>59</v>
       </c>
@@ -3730,10 +3702,8 @@
       <c r="AR28" s="8"/>
       <c r="AS28" s="8"/>
       <c r="AT28" s="8"/>
-      <c r="AU28" s="8"/>
-      <c r="AV28" s="8"/>
-    </row>
-    <row r="29" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>61</v>
       </c>
@@ -3786,7 +3756,7 @@
         <v>46.068000000000005</v>
       </c>
       <c r="R29" s="4">
-        <f t="shared" ref="R28:R43" si="10">14*Q29-P29-O29-F29</f>
+        <f t="shared" ref="R29:R42" si="10">14*Q29-P29-O29-F29</f>
         <v>92.038000000000125</v>
       </c>
       <c r="S29" s="8">
@@ -3838,10 +3808,8 @@
       <c r="AR29" s="8"/>
       <c r="AS29" s="8"/>
       <c r="AT29" s="8"/>
-      <c r="AU29" s="8"/>
-      <c r="AV29" s="8"/>
-    </row>
-    <row r="30" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>62</v>
       </c>
@@ -3945,10 +3913,8 @@
       <c r="AR30" s="8"/>
       <c r="AS30" s="8"/>
       <c r="AT30" s="8"/>
-      <c r="AU30" s="8"/>
-      <c r="AV30" s="8"/>
-    </row>
-    <row r="31" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>63</v>
       </c>
@@ -4051,10 +4017,8 @@
       <c r="AR31" s="8"/>
       <c r="AS31" s="8"/>
       <c r="AT31" s="8"/>
-      <c r="AU31" s="8"/>
-      <c r="AV31" s="8"/>
-    </row>
-    <row r="32" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>64</v>
       </c>
@@ -4153,10 +4117,8 @@
       <c r="AR32" s="8"/>
       <c r="AS32" s="8"/>
       <c r="AT32" s="8"/>
-      <c r="AU32" s="8"/>
-      <c r="AV32" s="8"/>
-    </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>65</v>
       </c>
@@ -4262,10 +4224,8 @@
       <c r="AR33" s="8"/>
       <c r="AS33" s="8"/>
       <c r="AT33" s="8"/>
-      <c r="AU33" s="8"/>
-      <c r="AV33" s="8"/>
-    </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>66</v>
       </c>
@@ -4371,10 +4331,8 @@
       <c r="AR34" s="8"/>
       <c r="AS34" s="8"/>
       <c r="AT34" s="8"/>
-      <c r="AU34" s="8"/>
-      <c r="AV34" s="8"/>
-    </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>67</v>
       </c>
@@ -4480,10 +4438,8 @@
       <c r="AR35" s="8"/>
       <c r="AS35" s="8"/>
       <c r="AT35" s="8"/>
-      <c r="AU35" s="8"/>
-      <c r="AV35" s="8"/>
-    </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>68</v>
       </c>
@@ -4582,10 +4538,8 @@
       <c r="AR36" s="8"/>
       <c r="AS36" s="8"/>
       <c r="AT36" s="8"/>
-      <c r="AU36" s="8"/>
-      <c r="AV36" s="8"/>
-    </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>69</v>
       </c>
@@ -4607,7 +4561,9 @@
       <c r="G37" s="6">
         <v>1</v>
       </c>
-      <c r="H37" s="8"/>
+      <c r="H37" s="8">
+        <v>45</v>
+      </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8">
@@ -4683,10 +4639,8 @@
       <c r="AR37" s="8"/>
       <c r="AS37" s="8"/>
       <c r="AT37" s="8"/>
-      <c r="AU37" s="8"/>
-      <c r="AV37" s="8"/>
-    </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>70</v>
       </c>
@@ -4708,7 +4662,9 @@
       <c r="G38" s="6">
         <v>0.4</v>
       </c>
-      <c r="H38" s="8"/>
+      <c r="H38" s="8">
+        <v>45</v>
+      </c>
       <c r="I38" s="8">
         <v>6475</v>
       </c>
@@ -4783,10 +4739,8 @@
       <c r="AR38" s="8"/>
       <c r="AS38" s="8"/>
       <c r="AT38" s="8"/>
-      <c r="AU38" s="8"/>
-      <c r="AV38" s="8"/>
-    </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>71</v>
       </c>
@@ -4808,8 +4762,8 @@
       <c r="G39" s="6">
         <v>0.3</v>
       </c>
-      <c r="H39" s="8" t="e">
-        <v>#N/A</v>
+      <c r="H39" s="8">
+        <v>45</v>
       </c>
       <c r="I39" s="8">
         <v>6495</v>
@@ -4885,10 +4839,8 @@
       <c r="AR39" s="8"/>
       <c r="AS39" s="8"/>
       <c r="AT39" s="8"/>
-      <c r="AU39" s="8"/>
-      <c r="AV39" s="8"/>
-    </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>72</v>
       </c>
@@ -4994,10 +4946,8 @@
       <c r="AR40" s="8"/>
       <c r="AS40" s="8"/>
       <c r="AT40" s="8"/>
-      <c r="AU40" s="8"/>
-      <c r="AV40" s="8"/>
-    </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>73</v>
       </c>
@@ -5099,10 +5049,8 @@
       <c r="AR41" s="8"/>
       <c r="AS41" s="8"/>
       <c r="AT41" s="8"/>
-      <c r="AU41" s="8"/>
-      <c r="AV41" s="8"/>
-    </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>74</v>
       </c>
@@ -5208,10 +5156,8 @@
       <c r="AR42" s="8"/>
       <c r="AS42" s="8"/>
       <c r="AT42" s="8"/>
-      <c r="AU42" s="8"/>
-      <c r="AV42" s="8"/>
-    </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>75</v>
       </c>
@@ -5314,10 +5260,8 @@
       <c r="AR43" s="8"/>
       <c r="AS43" s="8"/>
       <c r="AT43" s="8"/>
-      <c r="AU43" s="8"/>
-      <c r="AV43" s="8"/>
-    </row>
-    <row r="44" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>76</v>
       </c>
@@ -5407,10 +5351,8 @@
       <c r="AR44" s="8"/>
       <c r="AS44" s="8"/>
       <c r="AT44" s="8"/>
-      <c r="AU44" s="8"/>
-      <c r="AV44" s="8"/>
-    </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>78</v>
       </c>
@@ -5511,10 +5453,8 @@
       <c r="AR45" s="8"/>
       <c r="AS45" s="8"/>
       <c r="AT45" s="8"/>
-      <c r="AU45" s="8"/>
-      <c r="AV45" s="8"/>
-    </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>79</v>
       </c>
@@ -5613,10 +5553,8 @@
       <c r="AR46" s="8"/>
       <c r="AS46" s="8"/>
       <c r="AT46" s="8"/>
-      <c r="AU46" s="8"/>
-      <c r="AV46" s="8"/>
-    </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>80</v>
       </c>
@@ -5670,7 +5608,7 @@
         <v>238</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" ref="R45:R49" si="16">14*Q47-P47-O47-F47</f>
+        <f t="shared" ref="R47:R49" si="16">14*Q47-P47-O47-F47</f>
         <v>1461</v>
       </c>
       <c r="S47" s="8">
@@ -5722,10 +5660,8 @@
       <c r="AR47" s="8"/>
       <c r="AS47" s="8"/>
       <c r="AT47" s="8"/>
-      <c r="AU47" s="8"/>
-      <c r="AV47" s="8"/>
-    </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>81</v>
       </c>
@@ -5829,10 +5765,8 @@
       <c r="AR48" s="8"/>
       <c r="AS48" s="8"/>
       <c r="AT48" s="8"/>
-      <c r="AU48" s="8"/>
-      <c r="AV48" s="8"/>
-    </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>82</v>
       </c>
@@ -5934,10 +5868,8 @@
       <c r="AR49" s="8"/>
       <c r="AS49" s="8"/>
       <c r="AT49" s="8"/>
-      <c r="AU49" s="8"/>
-      <c r="AV49" s="8"/>
-    </row>
-    <row r="50" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>83</v>
       </c>
@@ -6027,10 +5959,8 @@
       <c r="AR50" s="8"/>
       <c r="AS50" s="8"/>
       <c r="AT50" s="8"/>
-      <c r="AU50" s="8"/>
-      <c r="AV50" s="8"/>
-    </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>84</v>
       </c>
@@ -6136,10 +6066,8 @@
       <c r="AR51" s="8"/>
       <c r="AS51" s="8"/>
       <c r="AT51" s="8"/>
-      <c r="AU51" s="8"/>
-      <c r="AV51" s="8"/>
-    </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>85</v>
       </c>
@@ -6243,10 +6171,8 @@
       <c r="AR52" s="8"/>
       <c r="AS52" s="8"/>
       <c r="AT52" s="8"/>
-      <c r="AU52" s="8"/>
-      <c r="AV52" s="8"/>
-    </row>
-    <row r="53" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>86</v>
       </c>
@@ -6264,9 +6190,7 @@
       <c r="G53" s="11">
         <v>0</v>
       </c>
-      <c r="H53" s="10">
-        <v>45</v>
-      </c>
+      <c r="H53" s="10"/>
       <c r="I53" s="10" t="s">
         <v>87</v>
       </c>
@@ -6340,10 +6264,8 @@
       <c r="AR53" s="8"/>
       <c r="AS53" s="8"/>
       <c r="AT53" s="8"/>
-      <c r="AU53" s="8"/>
-      <c r="AV53" s="8"/>
-    </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>89</v>
       </c>
@@ -6365,8 +6287,8 @@
       <c r="G54" s="6">
         <v>0.4</v>
       </c>
-      <c r="H54" s="8" t="e">
-        <v>#N/A</v>
+      <c r="H54" s="8">
+        <v>60</v>
       </c>
       <c r="I54" s="8">
         <v>6797</v>
@@ -6446,10 +6368,8 @@
       <c r="AR54" s="8"/>
       <c r="AS54" s="8"/>
       <c r="AT54" s="8"/>
-      <c r="AU54" s="8"/>
-      <c r="AV54" s="8"/>
-    </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>90</v>
       </c>
@@ -6550,10 +6470,8 @@
       <c r="AR55" s="8"/>
       <c r="AS55" s="8"/>
       <c r="AT55" s="8"/>
-      <c r="AU55" s="8"/>
-      <c r="AV55" s="8"/>
-    </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>91</v>
       </c>
@@ -6656,10 +6574,8 @@
       <c r="AR56" s="8"/>
       <c r="AS56" s="8"/>
       <c r="AT56" s="8"/>
-      <c r="AU56" s="8"/>
-      <c r="AV56" s="8"/>
-    </row>
-    <row r="57" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>92</v>
       </c>
@@ -6681,7 +6597,9 @@
       <c r="G57" s="6">
         <v>1</v>
       </c>
-      <c r="H57" s="8"/>
+      <c r="H57" s="8">
+        <v>30</v>
+      </c>
       <c r="I57" s="8">
         <v>6832</v>
       </c>
@@ -6759,10 +6677,8 @@
       <c r="AR57" s="8"/>
       <c r="AS57" s="8"/>
       <c r="AT57" s="8"/>
-      <c r="AU57" s="8"/>
-      <c r="AV57" s="8"/>
-    </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>93</v>
       </c>
@@ -6857,10 +6773,8 @@
       <c r="AR58" s="8"/>
       <c r="AS58" s="8"/>
       <c r="AT58" s="8"/>
-      <c r="AU58" s="8"/>
-      <c r="AV58" s="8"/>
-    </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>94</v>
       </c>
@@ -6959,10 +6873,8 @@
       <c r="AR59" s="8"/>
       <c r="AS59" s="8"/>
       <c r="AT59" s="8"/>
-      <c r="AU59" s="8"/>
-      <c r="AV59" s="8"/>
-    </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>95</v>
       </c>
@@ -7061,10 +6973,8 @@
       <c r="AR60" s="8"/>
       <c r="AS60" s="8"/>
       <c r="AT60" s="8"/>
-      <c r="AU60" s="8"/>
-      <c r="AV60" s="8"/>
-    </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>96</v>
       </c>
@@ -7114,7 +7024,7 @@
         <v>3.62</v>
       </c>
       <c r="R61" s="4">
-        <f t="shared" ref="R54:R62" si="19">14*Q61-P61-O61-F61</f>
+        <f t="shared" ref="R61" si="19">14*Q61-P61-O61-F61</f>
         <v>16.094999999999999</v>
       </c>
       <c r="S61" s="8">
@@ -7166,10 +7076,8 @@
       <c r="AR61" s="8"/>
       <c r="AS61" s="8"/>
       <c r="AT61" s="8"/>
-      <c r="AU61" s="8"/>
-      <c r="AV61" s="8"/>
-    </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>97</v>
       </c>
@@ -7189,7 +7097,9 @@
       <c r="G62" s="6">
         <v>0.6</v>
       </c>
-      <c r="H62" s="8"/>
+      <c r="H62" s="8">
+        <v>45</v>
+      </c>
       <c r="I62" s="8">
         <v>6925</v>
       </c>
@@ -7262,10 +7172,8 @@
       <c r="AR62" s="8"/>
       <c r="AS62" s="8"/>
       <c r="AT62" s="8"/>
-      <c r="AU62" s="8"/>
-      <c r="AV62" s="8"/>
-    </row>
-    <row r="63" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>98</v>
       </c>
@@ -7355,10 +7263,8 @@
       <c r="AR63" s="8"/>
       <c r="AS63" s="8"/>
       <c r="AT63" s="8"/>
-      <c r="AU63" s="8"/>
-      <c r="AV63" s="8"/>
-    </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>99</v>
       </c>
@@ -7380,7 +7286,9 @@
       <c r="G64" s="6">
         <v>1</v>
       </c>
-      <c r="H64" s="8"/>
+      <c r="H64" s="8">
+        <v>45</v>
+      </c>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8">
@@ -7455,10 +7363,8 @@
       <c r="AR64" s="8"/>
       <c r="AS64" s="8"/>
       <c r="AT64" s="8"/>
-      <c r="AU64" s="8"/>
-      <c r="AV64" s="8"/>
-    </row>
-    <row r="65" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>100</v>
       </c>
@@ -7510,7 +7416,7 @@
         <v>10</v>
       </c>
       <c r="R65" s="4">
-        <f t="shared" ref="R64:R68" si="20">14*Q65-P65-O65-F65</f>
+        <f t="shared" ref="R65:R67" si="20">14*Q65-P65-O65-F65</f>
         <v>32</v>
       </c>
       <c r="S65" s="8">
@@ -7562,10 +7468,8 @@
       <c r="AR65" s="8"/>
       <c r="AS65" s="8"/>
       <c r="AT65" s="8"/>
-      <c r="AU65" s="8"/>
-      <c r="AV65" s="8"/>
-    </row>
-    <row r="66" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>101</v>
       </c>
@@ -7667,10 +7571,8 @@
       <c r="AR66" s="8"/>
       <c r="AS66" s="8"/>
       <c r="AT66" s="8"/>
-      <c r="AU66" s="8"/>
-      <c r="AV66" s="8"/>
-    </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>102</v>
       </c>
@@ -7692,7 +7594,9 @@
       <c r="G67" s="6">
         <v>0.3</v>
       </c>
-      <c r="H67" s="8"/>
+      <c r="H67" s="8">
+        <v>60</v>
+      </c>
       <c r="I67" s="8">
         <v>7059</v>
       </c>
@@ -7770,10 +7674,8 @@
       <c r="AR67" s="8"/>
       <c r="AS67" s="8"/>
       <c r="AT67" s="8"/>
-      <c r="AU67" s="8"/>
-      <c r="AV67" s="8"/>
-    </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>103</v>
       </c>
@@ -7879,10 +7781,8 @@
       <c r="AR68" s="8"/>
       <c r="AS68" s="8"/>
       <c r="AT68" s="8"/>
-      <c r="AU68" s="8"/>
-      <c r="AV68" s="8"/>
-    </row>
-    <row r="69" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>104</v>
       </c>
@@ -7978,10 +7878,8 @@
       <c r="AR69" s="8"/>
       <c r="AS69" s="8"/>
       <c r="AT69" s="8"/>
-      <c r="AU69" s="8"/>
-      <c r="AV69" s="8"/>
-    </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>105</v>
       </c>
@@ -8037,7 +7935,7 @@
         <v>67.328400000000002</v>
       </c>
       <c r="R70" s="4">
-        <f t="shared" ref="R70:R72" si="24">14*Q70-P70-O70-F70</f>
+        <f t="shared" ref="R70:R71" si="24">14*Q70-P70-O70-F70</f>
         <v>136.26160000000004</v>
       </c>
       <c r="S70" s="8">
@@ -8089,10 +7987,8 @@
       <c r="AR70" s="8"/>
       <c r="AS70" s="8"/>
       <c r="AT70" s="8"/>
-      <c r="AU70" s="8"/>
-      <c r="AV70" s="8"/>
-    </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>106</v>
       </c>
@@ -8194,10 +8090,8 @@
       <c r="AR71" s="8"/>
       <c r="AS71" s="8"/>
       <c r="AT71" s="8"/>
-      <c r="AU71" s="8"/>
-      <c r="AV71" s="8"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>107</v>
       </c>
@@ -8222,8 +8116,8 @@
       <c r="H72" s="8">
         <v>50</v>
       </c>
-      <c r="I72" s="8">
-        <v>7080</v>
+      <c r="I72" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="8">
@@ -8250,10 +8144,12 @@
         <f t="shared" si="23"/>
         <v>48</v>
       </c>
-      <c r="R72" s="4"/>
+      <c r="R72" s="19">
+        <v>600</v>
+      </c>
       <c r="S72" s="8">
         <f t="shared" si="25"/>
-        <v>32.520833333333336</v>
+        <v>45.020833333333336</v>
       </c>
       <c r="T72" s="8">
         <f t="shared" si="26"/>
@@ -8278,11 +8174,11 @@
         <v>136.80000000000001</v>
       </c>
       <c r="AA72" s="16" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="AB72" s="8">
         <f>G72*R72</f>
-        <v>0</v>
+        <v>245.99999999999997</v>
       </c>
       <c r="AC72" s="8"/>
       <c r="AD72" s="8"/>
@@ -8302,10 +8198,8 @@
       <c r="AR72" s="8"/>
       <c r="AS72" s="8"/>
       <c r="AT72" s="8"/>
-      <c r="AU72" s="8"/>
-      <c r="AV72" s="8"/>
-    </row>
-    <row r="73" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>108</v>
       </c>
@@ -8395,10 +8289,8 @@
       <c r="AR73" s="8"/>
       <c r="AS73" s="8"/>
       <c r="AT73" s="8"/>
-      <c r="AU73" s="8"/>
-      <c r="AV73" s="8"/>
-    </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>109</v>
       </c>
@@ -8422,7 +8314,9 @@
       <c r="G74" s="6">
         <v>1</v>
       </c>
-      <c r="H74" s="8"/>
+      <c r="H74" s="8">
+        <v>50</v>
+      </c>
       <c r="I74" s="8">
         <v>7083</v>
       </c>
@@ -8499,10 +8393,8 @@
       <c r="AR74" s="8"/>
       <c r="AS74" s="8"/>
       <c r="AT74" s="8"/>
-      <c r="AU74" s="8"/>
-      <c r="AV74" s="8"/>
-    </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>110</v>
       </c>
@@ -8599,10 +8491,8 @@
       <c r="AR75" s="8"/>
       <c r="AS75" s="8"/>
       <c r="AT75" s="8"/>
-      <c r="AU75" s="8"/>
-      <c r="AV75" s="8"/>
-    </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>111</v>
       </c>
@@ -8656,7 +8546,7 @@
         <v>48.4</v>
       </c>
       <c r="R76" s="4">
-        <f t="shared" ref="R74:R77" si="27">14*Q76-P76-O76-F76</f>
+        <f t="shared" ref="R76" si="27">14*Q76-P76-O76-F76</f>
         <v>312.60000000000002</v>
       </c>
       <c r="S76" s="8">
@@ -8708,10 +8598,8 @@
       <c r="AR76" s="8"/>
       <c r="AS76" s="8"/>
       <c r="AT76" s="8"/>
-      <c r="AU76" s="8"/>
-      <c r="AV76" s="8"/>
-    </row>
-    <row r="77" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>112</v>
       </c>
@@ -8810,10 +8698,8 @@
       <c r="AR77" s="8"/>
       <c r="AS77" s="8"/>
       <c r="AT77" s="8"/>
-      <c r="AU77" s="8"/>
-      <c r="AV77" s="8"/>
-    </row>
-    <row r="78" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>113</v>
       </c>
@@ -8903,10 +8789,8 @@
       <c r="AR78" s="8"/>
       <c r="AS78" s="8"/>
       <c r="AT78" s="8"/>
-      <c r="AU78" s="8"/>
-      <c r="AV78" s="8"/>
-    </row>
-    <row r="79" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>114</v>
       </c>
@@ -8960,7 +8844,7 @@
         <v>175.6</v>
       </c>
       <c r="R79" s="4">
-        <f t="shared" ref="R79:R90" si="28">14*Q79-P79-O79-F79</f>
+        <f t="shared" ref="R79:R89" si="28">14*Q79-P79-O79-F79</f>
         <v>1084.4000000000001</v>
       </c>
       <c r="S79" s="8">
@@ -9012,10 +8896,8 @@
       <c r="AR79" s="8"/>
       <c r="AS79" s="8"/>
       <c r="AT79" s="8"/>
-      <c r="AU79" s="8"/>
-      <c r="AV79" s="8"/>
-    </row>
-    <row r="80" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>115</v>
       </c>
@@ -9121,10 +9003,8 @@
       <c r="AR80" s="8"/>
       <c r="AS80" s="8"/>
       <c r="AT80" s="8"/>
-      <c r="AU80" s="8"/>
-      <c r="AV80" s="8"/>
-    </row>
-    <row r="81" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>116</v>
       </c>
@@ -9142,7 +9022,9 @@
       <c r="G81" s="6">
         <v>0.62</v>
       </c>
-      <c r="H81" s="8"/>
+      <c r="H81" s="8">
+        <v>50</v>
+      </c>
       <c r="I81" s="8">
         <v>7163</v>
       </c>
@@ -9217,10 +9099,8 @@
       <c r="AR81" s="8"/>
       <c r="AS81" s="8"/>
       <c r="AT81" s="8"/>
-      <c r="AU81" s="8"/>
-      <c r="AV81" s="8"/>
-    </row>
-    <row r="82" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>117</v>
       </c>
@@ -9326,10 +9206,8 @@
       <c r="AR82" s="8"/>
       <c r="AS82" s="8"/>
       <c r="AT82" s="8"/>
-      <c r="AU82" s="8"/>
-      <c r="AV82" s="8"/>
-    </row>
-    <row r="83" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>118</v>
       </c>
@@ -9435,10 +9313,8 @@
       <c r="AR83" s="8"/>
       <c r="AS83" s="8"/>
       <c r="AT83" s="8"/>
-      <c r="AU83" s="8"/>
-      <c r="AV83" s="8"/>
-    </row>
-    <row r="84" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
         <v>119</v>
       </c>
@@ -9542,10 +9418,8 @@
       <c r="AR84" s="8"/>
       <c r="AS84" s="8"/>
       <c r="AT84" s="8"/>
-      <c r="AU84" s="8"/>
-      <c r="AV84" s="8"/>
-    </row>
-    <row r="85" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>120</v>
       </c>
@@ -9646,10 +9520,8 @@
       <c r="AR85" s="8"/>
       <c r="AS85" s="8"/>
       <c r="AT85" s="8"/>
-      <c r="AU85" s="8"/>
-      <c r="AV85" s="8"/>
-    </row>
-    <row r="86" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>121</v>
       </c>
@@ -9755,10 +9627,8 @@
       <c r="AR86" s="8"/>
       <c r="AS86" s="8"/>
       <c r="AT86" s="8"/>
-      <c r="AU86" s="8"/>
-      <c r="AV86" s="8"/>
-    </row>
-    <row r="87" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>122</v>
       </c>
@@ -9862,10 +9732,8 @@
       <c r="AR87" s="8"/>
       <c r="AS87" s="8"/>
       <c r="AT87" s="8"/>
-      <c r="AU87" s="8"/>
-      <c r="AV87" s="8"/>
-    </row>
-    <row r="88" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>123</v>
       </c>
@@ -9967,10 +9835,8 @@
       <c r="AR88" s="8"/>
       <c r="AS88" s="8"/>
       <c r="AT88" s="8"/>
-      <c r="AU88" s="8"/>
-      <c r="AV88" s="8"/>
-    </row>
-    <row r="89" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
         <v>124</v>
       </c>
@@ -10072,10 +9938,8 @@
       <c r="AR89" s="8"/>
       <c r="AS89" s="8"/>
       <c r="AT89" s="8"/>
-      <c r="AU89" s="8"/>
-      <c r="AV89" s="8"/>
-    </row>
-    <row r="90" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
         <v>125</v>
       </c>
@@ -10178,10 +10042,8 @@
       <c r="AR90" s="8"/>
       <c r="AS90" s="8"/>
       <c r="AT90" s="8"/>
-      <c r="AU90" s="8"/>
-      <c r="AV90" s="8"/>
-    </row>
-    <row r="91" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>126</v>
       </c>
@@ -10271,10 +10133,8 @@
       <c r="AR91" s="8"/>
       <c r="AS91" s="8"/>
       <c r="AT91" s="8"/>
-      <c r="AU91" s="8"/>
-      <c r="AV91" s="8"/>
-    </row>
-    <row r="92" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
         <v>127</v>
       </c>
@@ -10296,7 +10156,9 @@
       <c r="G92" s="6">
         <v>0.3</v>
       </c>
-      <c r="H92" s="8"/>
+      <c r="H92" s="8">
+        <v>50</v>
+      </c>
       <c r="I92" s="8">
         <v>7276</v>
       </c>
@@ -10373,10 +10235,8 @@
       <c r="AR92" s="8"/>
       <c r="AS92" s="8"/>
       <c r="AT92" s="8"/>
-      <c r="AU92" s="8"/>
-      <c r="AV92" s="8"/>
-    </row>
-    <row r="93" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
         <v>128</v>
       </c>
@@ -10475,10 +10335,8 @@
       <c r="AR93" s="8"/>
       <c r="AS93" s="8"/>
       <c r="AT93" s="8"/>
-      <c r="AU93" s="8"/>
-      <c r="AV93" s="8"/>
-    </row>
-    <row r="94" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
         <v>129</v>
       </c>
@@ -10579,10 +10437,8 @@
       <c r="AR94" s="8"/>
       <c r="AS94" s="8"/>
       <c r="AT94" s="8"/>
-      <c r="AU94" s="8"/>
-      <c r="AV94" s="8"/>
-    </row>
-    <row r="95" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>130</v>
       </c>
@@ -10632,7 +10488,7 @@
         <v>3.8</v>
       </c>
       <c r="R95" s="4">
-        <f t="shared" ref="R92:R101" si="31">14*Q95-P95-O95-F95</f>
+        <f t="shared" ref="R95" si="31">14*Q95-P95-O95-F95</f>
         <v>33.199999999999996</v>
       </c>
       <c r="S95" s="8">
@@ -10684,10 +10540,8 @@
       <c r="AR95" s="8"/>
       <c r="AS95" s="8"/>
       <c r="AT95" s="8"/>
-      <c r="AU95" s="8"/>
-      <c r="AV95" s="8"/>
-    </row>
-    <row r="96" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
         <v>131</v>
       </c>
@@ -10788,10 +10642,8 @@
       <c r="AR96" s="8"/>
       <c r="AS96" s="8"/>
       <c r="AT96" s="8"/>
-      <c r="AU96" s="8"/>
-      <c r="AV96" s="8"/>
-    </row>
-    <row r="97" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
         <v>132</v>
       </c>
@@ -10813,7 +10665,9 @@
       <c r="G97" s="6">
         <v>0.3</v>
       </c>
-      <c r="H97" s="8"/>
+      <c r="H97" s="8">
+        <v>45</v>
+      </c>
       <c r="I97" s="8">
         <v>7371</v>
       </c>
@@ -10890,10 +10744,8 @@
       <c r="AR97" s="8"/>
       <c r="AS97" s="8"/>
       <c r="AT97" s="8"/>
-      <c r="AU97" s="8"/>
-      <c r="AV97" s="8"/>
-    </row>
-    <row r="98" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>133</v>
       </c>
@@ -10944,12 +10796,13 @@
         <f t="shared" si="23"/>
         <v>98</v>
       </c>
-      <c r="R98" s="4">
-        <v>160</v>
+      <c r="R98" s="18">
+        <f>160+400</f>
+        <v>560</v>
       </c>
       <c r="S98" s="8">
         <f t="shared" si="25"/>
-        <v>8.7857142857142865</v>
+        <v>12.86734693877551</v>
       </c>
       <c r="T98" s="8">
         <f t="shared" si="26"/>
@@ -10973,10 +10826,12 @@
       <c r="Z98" s="8">
         <v>34.200000000000003</v>
       </c>
-      <c r="AA98" s="8"/>
+      <c r="AA98" s="16" t="s">
+        <v>146</v>
+      </c>
       <c r="AB98" s="8">
         <f t="shared" si="30"/>
-        <v>19.2</v>
+        <v>67.2</v>
       </c>
       <c r="AC98" s="8"/>
       <c r="AD98" s="8"/>
@@ -10996,10 +10851,8 @@
       <c r="AR98" s="8"/>
       <c r="AS98" s="8"/>
       <c r="AT98" s="8"/>
-      <c r="AU98" s="8"/>
-      <c r="AV98" s="8"/>
-    </row>
-    <row r="99" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>134</v>
       </c>
@@ -11021,7 +10874,9 @@
       <c r="G99" s="6">
         <v>0.33</v>
       </c>
-      <c r="H99" s="8"/>
+      <c r="H99" s="8">
+        <v>30</v>
+      </c>
       <c r="I99" s="8">
         <v>7461</v>
       </c>
@@ -11099,10 +10954,8 @@
       <c r="AR99" s="8"/>
       <c r="AS99" s="8"/>
       <c r="AT99" s="8"/>
-      <c r="AU99" s="8"/>
-      <c r="AV99" s="8"/>
-    </row>
-    <row r="100" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>135</v>
       </c>
@@ -11122,7 +10975,9 @@
       <c r="G100" s="6">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H100" s="8"/>
+      <c r="H100" s="8">
+        <v>45</v>
+      </c>
       <c r="I100" s="8"/>
       <c r="J100" s="8"/>
       <c r="K100" s="8">
@@ -11197,10 +11052,8 @@
       <c r="AR100" s="8"/>
       <c r="AS100" s="8"/>
       <c r="AT100" s="8"/>
-      <c r="AU100" s="8"/>
-      <c r="AV100" s="8"/>
-    </row>
-    <row r="101" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
         <v>58</v>
       </c>
@@ -11224,7 +11077,9 @@
       <c r="G101" s="6">
         <v>0.4</v>
       </c>
-      <c r="H101" s="8"/>
+      <c r="H101" s="8">
+        <v>60</v>
+      </c>
       <c r="I101" s="8">
         <v>7523</v>
       </c>
@@ -11301,10 +11156,8 @@
       <c r="AR101" s="8"/>
       <c r="AS101" s="8"/>
       <c r="AT101" s="8"/>
-      <c r="AU101" s="8"/>
-      <c r="AV101" s="8"/>
-    </row>
-    <row r="102" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>136</v>
       </c>
@@ -11331,11 +11184,11 @@
         <v>41</v>
       </c>
       <c r="L102" s="10">
-        <f t="shared" ref="L102:L133" si="32">E102-K102</f>
+        <f t="shared" ref="L102:L108" si="32">E102-K102</f>
         <v>-17</v>
       </c>
       <c r="M102" s="10">
-        <f t="shared" ref="M102:M133" si="33">E102-N102</f>
+        <f t="shared" ref="M102:M108" si="33">E102-N102</f>
         <v>0</v>
       </c>
       <c r="N102" s="10">
@@ -11351,7 +11204,7 @@
       </c>
       <c r="R102" s="13"/>
       <c r="S102" s="10" t="e">
-        <f t="shared" ref="S102:S133" si="35">(F102+O102+P102+R102)/Q102</f>
+        <f t="shared" ref="S102:S108" si="35">(F102+O102+P102+R102)/Q102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T102" s="10" t="e">
@@ -11396,10 +11249,8 @@
       <c r="AR102" s="8"/>
       <c r="AS102" s="8"/>
       <c r="AT102" s="8"/>
-      <c r="AU102" s="8"/>
-      <c r="AV102" s="8"/>
-    </row>
-    <row r="103" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
         <v>137</v>
       </c>
@@ -11421,7 +11272,9 @@
       <c r="G103" s="6">
         <v>1</v>
       </c>
-      <c r="H103" s="8"/>
+      <c r="H103" s="8">
+        <v>45</v>
+      </c>
       <c r="I103" s="8">
         <v>7564</v>
       </c>
@@ -11498,10 +11351,8 @@
       <c r="AR103" s="8"/>
       <c r="AS103" s="8"/>
       <c r="AT103" s="8"/>
-      <c r="AU103" s="8"/>
-      <c r="AV103" s="8"/>
-    </row>
-    <row r="104" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>88</v>
       </c>
@@ -11523,7 +11374,9 @@
       <c r="G104" s="6">
         <v>0.33</v>
       </c>
-      <c r="H104" s="8"/>
+      <c r="H104" s="8">
+        <v>45</v>
+      </c>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
       <c r="K104" s="8">
@@ -11602,10 +11455,8 @@
       <c r="AR104" s="8"/>
       <c r="AS104" s="8"/>
       <c r="AT104" s="8"/>
-      <c r="AU104" s="8"/>
-      <c r="AV104" s="8"/>
-    </row>
-    <row r="105" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
         <v>140</v>
       </c>
@@ -11695,10 +11546,8 @@
       <c r="AR105" s="8"/>
       <c r="AS105" s="8"/>
       <c r="AT105" s="8"/>
-      <c r="AU105" s="8"/>
-      <c r="AV105" s="8"/>
-    </row>
-    <row r="106" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
         <v>141</v>
       </c>
@@ -11786,10 +11635,8 @@
       <c r="AR106" s="8"/>
       <c r="AS106" s="8"/>
       <c r="AT106" s="8"/>
-      <c r="AU106" s="8"/>
-      <c r="AV106" s="8"/>
-    </row>
-    <row r="107" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
         <v>143</v>
       </c>
@@ -11885,10 +11732,8 @@
       <c r="AR107" s="8"/>
       <c r="AS107" s="8"/>
       <c r="AT107" s="8"/>
-      <c r="AU107" s="8"/>
-      <c r="AV107" s="8"/>
-    </row>
-    <row r="108" spans="1:48" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>144</v>
       </c>
@@ -11984,10 +11829,8 @@
       <c r="AR108" s="8"/>
       <c r="AS108" s="8"/>
       <c r="AT108" s="8"/>
-      <c r="AU108" s="8"/>
-      <c r="AV108" s="8"/>
-    </row>
-    <row r="109" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -12034,10 +11877,8 @@
       <c r="AR109" s="8"/>
       <c r="AS109" s="8"/>
       <c r="AT109" s="8"/>
-      <c r="AU109" s="8"/>
-      <c r="AV109" s="8"/>
-    </row>
-    <row r="110" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -12084,10 +11925,8 @@
       <c r="AR110" s="8"/>
       <c r="AS110" s="8"/>
       <c r="AT110" s="8"/>
-      <c r="AU110" s="8"/>
-      <c r="AV110" s="8"/>
-    </row>
-    <row r="111" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -12134,10 +11973,8 @@
       <c r="AR111" s="8"/>
       <c r="AS111" s="8"/>
       <c r="AT111" s="8"/>
-      <c r="AU111" s="8"/>
-      <c r="AV111" s="8"/>
-    </row>
-    <row r="112" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -12184,10 +12021,8 @@
       <c r="AR112" s="8"/>
       <c r="AS112" s="8"/>
       <c r="AT112" s="8"/>
-      <c r="AU112" s="8"/>
-      <c r="AV112" s="8"/>
-    </row>
-    <row r="113" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
@@ -12234,10 +12069,8 @@
       <c r="AR113" s="8"/>
       <c r="AS113" s="8"/>
       <c r="AT113" s="8"/>
-      <c r="AU113" s="8"/>
-      <c r="AV113" s="8"/>
-    </row>
-    <row r="114" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A114" s="8"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
@@ -12284,10 +12117,8 @@
       <c r="AR114" s="8"/>
       <c r="AS114" s="8"/>
       <c r="AT114" s="8"/>
-      <c r="AU114" s="8"/>
-      <c r="AV114" s="8"/>
-    </row>
-    <row r="115" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A115" s="8"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
@@ -12334,10 +12165,8 @@
       <c r="AR115" s="8"/>
       <c r="AS115" s="8"/>
       <c r="AT115" s="8"/>
-      <c r="AU115" s="8"/>
-      <c r="AV115" s="8"/>
-    </row>
-    <row r="116" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A116" s="8"/>
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
@@ -12384,10 +12213,8 @@
       <c r="AR116" s="8"/>
       <c r="AS116" s="8"/>
       <c r="AT116" s="8"/>
-      <c r="AU116" s="8"/>
-      <c r="AV116" s="8"/>
-    </row>
-    <row r="117" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
@@ -12434,10 +12261,8 @@
       <c r="AR117" s="8"/>
       <c r="AS117" s="8"/>
       <c r="AT117" s="8"/>
-      <c r="AU117" s="8"/>
-      <c r="AV117" s="8"/>
-    </row>
-    <row r="118" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A118" s="8"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
@@ -12484,10 +12309,8 @@
       <c r="AR118" s="8"/>
       <c r="AS118" s="8"/>
       <c r="AT118" s="8"/>
-      <c r="AU118" s="8"/>
-      <c r="AV118" s="8"/>
-    </row>
-    <row r="119" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
@@ -12534,10 +12357,8 @@
       <c r="AR119" s="8"/>
       <c r="AS119" s="8"/>
       <c r="AT119" s="8"/>
-      <c r="AU119" s="8"/>
-      <c r="AV119" s="8"/>
-    </row>
-    <row r="120" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A120" s="8"/>
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
@@ -12584,10 +12405,8 @@
       <c r="AR120" s="8"/>
       <c r="AS120" s="8"/>
       <c r="AT120" s="8"/>
-      <c r="AU120" s="8"/>
-      <c r="AV120" s="8"/>
-    </row>
-    <row r="121" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
@@ -12634,10 +12453,8 @@
       <c r="AR121" s="8"/>
       <c r="AS121" s="8"/>
       <c r="AT121" s="8"/>
-      <c r="AU121" s="8"/>
-      <c r="AV121" s="8"/>
-    </row>
-    <row r="122" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A122" s="8"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
@@ -12684,10 +12501,8 @@
       <c r="AR122" s="8"/>
       <c r="AS122" s="8"/>
       <c r="AT122" s="8"/>
-      <c r="AU122" s="8"/>
-      <c r="AV122" s="8"/>
-    </row>
-    <row r="123" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A123" s="8"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
@@ -12734,10 +12549,8 @@
       <c r="AR123" s="8"/>
       <c r="AS123" s="8"/>
       <c r="AT123" s="8"/>
-      <c r="AU123" s="8"/>
-      <c r="AV123" s="8"/>
-    </row>
-    <row r="124" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A124" s="8"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
@@ -12784,10 +12597,8 @@
       <c r="AR124" s="8"/>
       <c r="AS124" s="8"/>
       <c r="AT124" s="8"/>
-      <c r="AU124" s="8"/>
-      <c r="AV124" s="8"/>
-    </row>
-    <row r="125" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
@@ -12834,10 +12645,8 @@
       <c r="AR125" s="8"/>
       <c r="AS125" s="8"/>
       <c r="AT125" s="8"/>
-      <c r="AU125" s="8"/>
-      <c r="AV125" s="8"/>
-    </row>
-    <row r="126" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
@@ -12884,10 +12693,8 @@
       <c r="AR126" s="8"/>
       <c r="AS126" s="8"/>
       <c r="AT126" s="8"/>
-      <c r="AU126" s="8"/>
-      <c r="AV126" s="8"/>
-    </row>
-    <row r="127" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
@@ -12934,10 +12741,8 @@
       <c r="AR127" s="8"/>
       <c r="AS127" s="8"/>
       <c r="AT127" s="8"/>
-      <c r="AU127" s="8"/>
-      <c r="AV127" s="8"/>
-    </row>
-    <row r="128" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A128" s="8"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
@@ -12984,10 +12789,8 @@
       <c r="AR128" s="8"/>
       <c r="AS128" s="8"/>
       <c r="AT128" s="8"/>
-      <c r="AU128" s="8"/>
-      <c r="AV128" s="8"/>
-    </row>
-    <row r="129" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
@@ -13034,10 +12837,8 @@
       <c r="AR129" s="8"/>
       <c r="AS129" s="8"/>
       <c r="AT129" s="8"/>
-      <c r="AU129" s="8"/>
-      <c r="AV129" s="8"/>
-    </row>
-    <row r="130" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A130" s="8"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
@@ -13084,10 +12885,8 @@
       <c r="AR130" s="8"/>
       <c r="AS130" s="8"/>
       <c r="AT130" s="8"/>
-      <c r="AU130" s="8"/>
-      <c r="AV130" s="8"/>
-    </row>
-    <row r="131" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
@@ -13134,10 +12933,8 @@
       <c r="AR131" s="8"/>
       <c r="AS131" s="8"/>
       <c r="AT131" s="8"/>
-      <c r="AU131" s="8"/>
-      <c r="AV131" s="8"/>
-    </row>
-    <row r="132" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A132" s="8"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -13184,10 +12981,8 @@
       <c r="AR132" s="8"/>
       <c r="AS132" s="8"/>
       <c r="AT132" s="8"/>
-      <c r="AU132" s="8"/>
-      <c r="AV132" s="8"/>
-    </row>
-    <row r="133" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -13234,10 +13029,8 @@
       <c r="AR133" s="8"/>
       <c r="AS133" s="8"/>
       <c r="AT133" s="8"/>
-      <c r="AU133" s="8"/>
-      <c r="AV133" s="8"/>
-    </row>
-    <row r="134" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A134" s="8"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -13284,10 +13077,8 @@
       <c r="AR134" s="8"/>
       <c r="AS134" s="8"/>
       <c r="AT134" s="8"/>
-      <c r="AU134" s="8"/>
-      <c r="AV134" s="8"/>
-    </row>
-    <row r="135" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -13334,10 +13125,8 @@
       <c r="AR135" s="8"/>
       <c r="AS135" s="8"/>
       <c r="AT135" s="8"/>
-      <c r="AU135" s="8"/>
-      <c r="AV135" s="8"/>
-    </row>
-    <row r="136" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A136" s="8"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -13384,10 +13173,8 @@
       <c r="AR136" s="8"/>
       <c r="AS136" s="8"/>
       <c r="AT136" s="8"/>
-      <c r="AU136" s="8"/>
-      <c r="AV136" s="8"/>
-    </row>
-    <row r="137" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -13434,10 +13221,8 @@
       <c r="AR137" s="8"/>
       <c r="AS137" s="8"/>
       <c r="AT137" s="8"/>
-      <c r="AU137" s="8"/>
-      <c r="AV137" s="8"/>
-    </row>
-    <row r="138" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -13484,10 +13269,8 @@
       <c r="AR138" s="8"/>
       <c r="AS138" s="8"/>
       <c r="AT138" s="8"/>
-      <c r="AU138" s="8"/>
-      <c r="AV138" s="8"/>
-    </row>
-    <row r="139" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
@@ -13534,10 +13317,8 @@
       <c r="AR139" s="8"/>
       <c r="AS139" s="8"/>
       <c r="AT139" s="8"/>
-      <c r="AU139" s="8"/>
-      <c r="AV139" s="8"/>
-    </row>
-    <row r="140" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
@@ -13584,10 +13365,8 @@
       <c r="AR140" s="8"/>
       <c r="AS140" s="8"/>
       <c r="AT140" s="8"/>
-      <c r="AU140" s="8"/>
-      <c r="AV140" s="8"/>
-    </row>
-    <row r="141" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
@@ -13634,10 +13413,8 @@
       <c r="AR141" s="8"/>
       <c r="AS141" s="8"/>
       <c r="AT141" s="8"/>
-      <c r="AU141" s="8"/>
-      <c r="AV141" s="8"/>
-    </row>
-    <row r="142" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
@@ -13684,10 +13461,8 @@
       <c r="AR142" s="8"/>
       <c r="AS142" s="8"/>
       <c r="AT142" s="8"/>
-      <c r="AU142" s="8"/>
-      <c r="AV142" s="8"/>
-    </row>
-    <row r="143" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
@@ -13734,10 +13509,8 @@
       <c r="AR143" s="8"/>
       <c r="AS143" s="8"/>
       <c r="AT143" s="8"/>
-      <c r="AU143" s="8"/>
-      <c r="AV143" s="8"/>
-    </row>
-    <row r="144" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A144" s="8"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
@@ -13784,10 +13557,8 @@
       <c r="AR144" s="8"/>
       <c r="AS144" s="8"/>
       <c r="AT144" s="8"/>
-      <c r="AU144" s="8"/>
-      <c r="AV144" s="8"/>
-    </row>
-    <row r="145" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
@@ -13834,10 +13605,8 @@
       <c r="AR145" s="8"/>
       <c r="AS145" s="8"/>
       <c r="AT145" s="8"/>
-      <c r="AU145" s="8"/>
-      <c r="AV145" s="8"/>
-    </row>
-    <row r="146" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
@@ -13884,10 +13653,8 @@
       <c r="AR146" s="8"/>
       <c r="AS146" s="8"/>
       <c r="AT146" s="8"/>
-      <c r="AU146" s="8"/>
-      <c r="AV146" s="8"/>
-    </row>
-    <row r="147" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -13934,10 +13701,8 @@
       <c r="AR147" s="8"/>
       <c r="AS147" s="8"/>
       <c r="AT147" s="8"/>
-      <c r="AU147" s="8"/>
-      <c r="AV147" s="8"/>
-    </row>
-    <row r="148" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
@@ -13984,10 +13749,8 @@
       <c r="AR148" s="8"/>
       <c r="AS148" s="8"/>
       <c r="AT148" s="8"/>
-      <c r="AU148" s="8"/>
-      <c r="AV148" s="8"/>
-    </row>
-    <row r="149" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -14034,10 +13797,8 @@
       <c r="AR149" s="8"/>
       <c r="AS149" s="8"/>
       <c r="AT149" s="8"/>
-      <c r="AU149" s="8"/>
-      <c r="AV149" s="8"/>
-    </row>
-    <row r="150" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -14084,10 +13845,8 @@
       <c r="AR150" s="8"/>
       <c r="AS150" s="8"/>
       <c r="AT150" s="8"/>
-      <c r="AU150" s="8"/>
-      <c r="AV150" s="8"/>
-    </row>
-    <row r="151" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -14134,10 +13893,8 @@
       <c r="AR151" s="8"/>
       <c r="AS151" s="8"/>
       <c r="AT151" s="8"/>
-      <c r="AU151" s="8"/>
-      <c r="AV151" s="8"/>
-    </row>
-    <row r="152" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -14184,10 +13941,8 @@
       <c r="AR152" s="8"/>
       <c r="AS152" s="8"/>
       <c r="AT152" s="8"/>
-      <c r="AU152" s="8"/>
-      <c r="AV152" s="8"/>
-    </row>
-    <row r="153" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -14234,10 +13989,8 @@
       <c r="AR153" s="8"/>
       <c r="AS153" s="8"/>
       <c r="AT153" s="8"/>
-      <c r="AU153" s="8"/>
-      <c r="AV153" s="8"/>
-    </row>
-    <row r="154" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -14284,10 +14037,8 @@
       <c r="AR154" s="8"/>
       <c r="AS154" s="8"/>
       <c r="AT154" s="8"/>
-      <c r="AU154" s="8"/>
-      <c r="AV154" s="8"/>
-    </row>
-    <row r="155" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -14334,10 +14085,8 @@
       <c r="AR155" s="8"/>
       <c r="AS155" s="8"/>
       <c r="AT155" s="8"/>
-      <c r="AU155" s="8"/>
-      <c r="AV155" s="8"/>
-    </row>
-    <row r="156" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -14384,10 +14133,8 @@
       <c r="AR156" s="8"/>
       <c r="AS156" s="8"/>
       <c r="AT156" s="8"/>
-      <c r="AU156" s="8"/>
-      <c r="AV156" s="8"/>
-    </row>
-    <row r="157" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -14434,10 +14181,8 @@
       <c r="AR157" s="8"/>
       <c r="AS157" s="8"/>
       <c r="AT157" s="8"/>
-      <c r="AU157" s="8"/>
-      <c r="AV157" s="8"/>
-    </row>
-    <row r="158" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -14484,10 +14229,8 @@
       <c r="AR158" s="8"/>
       <c r="AS158" s="8"/>
       <c r="AT158" s="8"/>
-      <c r="AU158" s="8"/>
-      <c r="AV158" s="8"/>
-    </row>
-    <row r="159" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -14534,10 +14277,8 @@
       <c r="AR159" s="8"/>
       <c r="AS159" s="8"/>
       <c r="AT159" s="8"/>
-      <c r="AU159" s="8"/>
-      <c r="AV159" s="8"/>
-    </row>
-    <row r="160" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -14584,10 +14325,8 @@
       <c r="AR160" s="8"/>
       <c r="AS160" s="8"/>
       <c r="AT160" s="8"/>
-      <c r="AU160" s="8"/>
-      <c r="AV160" s="8"/>
-    </row>
-    <row r="161" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -14634,10 +14373,8 @@
       <c r="AR161" s="8"/>
       <c r="AS161" s="8"/>
       <c r="AT161" s="8"/>
-      <c r="AU161" s="8"/>
-      <c r="AV161" s="8"/>
-    </row>
-    <row r="162" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -14684,10 +14421,8 @@
       <c r="AR162" s="8"/>
       <c r="AS162" s="8"/>
       <c r="AT162" s="8"/>
-      <c r="AU162" s="8"/>
-      <c r="AV162" s="8"/>
-    </row>
-    <row r="163" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -14734,10 +14469,8 @@
       <c r="AR163" s="8"/>
       <c r="AS163" s="8"/>
       <c r="AT163" s="8"/>
-      <c r="AU163" s="8"/>
-      <c r="AV163" s="8"/>
-    </row>
-    <row r="164" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A164" s="8"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -14784,10 +14517,8 @@
       <c r="AR164" s="8"/>
       <c r="AS164" s="8"/>
       <c r="AT164" s="8"/>
-      <c r="AU164" s="8"/>
-      <c r="AV164" s="8"/>
-    </row>
-    <row r="165" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
@@ -14834,10 +14565,8 @@
       <c r="AR165" s="8"/>
       <c r="AS165" s="8"/>
       <c r="AT165" s="8"/>
-      <c r="AU165" s="8"/>
-      <c r="AV165" s="8"/>
-    </row>
-    <row r="166" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
@@ -14884,10 +14613,8 @@
       <c r="AR166" s="8"/>
       <c r="AS166" s="8"/>
       <c r="AT166" s="8"/>
-      <c r="AU166" s="8"/>
-      <c r="AV166" s="8"/>
-    </row>
-    <row r="167" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
@@ -14934,10 +14661,8 @@
       <c r="AR167" s="8"/>
       <c r="AS167" s="8"/>
       <c r="AT167" s="8"/>
-      <c r="AU167" s="8"/>
-      <c r="AV167" s="8"/>
-    </row>
-    <row r="168" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
@@ -14984,10 +14709,8 @@
       <c r="AR168" s="8"/>
       <c r="AS168" s="8"/>
       <c r="AT168" s="8"/>
-      <c r="AU168" s="8"/>
-      <c r="AV168" s="8"/>
-    </row>
-    <row r="169" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
@@ -15034,10 +14757,8 @@
       <c r="AR169" s="8"/>
       <c r="AS169" s="8"/>
       <c r="AT169" s="8"/>
-      <c r="AU169" s="8"/>
-      <c r="AV169" s="8"/>
-    </row>
-    <row r="170" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
@@ -15084,10 +14805,8 @@
       <c r="AR170" s="8"/>
       <c r="AS170" s="8"/>
       <c r="AT170" s="8"/>
-      <c r="AU170" s="8"/>
-      <c r="AV170" s="8"/>
-    </row>
-    <row r="171" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
@@ -15134,10 +14853,8 @@
       <c r="AR171" s="8"/>
       <c r="AS171" s="8"/>
       <c r="AT171" s="8"/>
-      <c r="AU171" s="8"/>
-      <c r="AV171" s="8"/>
-    </row>
-    <row r="172" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
@@ -15184,10 +14901,8 @@
       <c r="AR172" s="8"/>
       <c r="AS172" s="8"/>
       <c r="AT172" s="8"/>
-      <c r="AU172" s="8"/>
-      <c r="AV172" s="8"/>
-    </row>
-    <row r="173" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
@@ -15234,10 +14949,8 @@
       <c r="AR173" s="8"/>
       <c r="AS173" s="8"/>
       <c r="AT173" s="8"/>
-      <c r="AU173" s="8"/>
-      <c r="AV173" s="8"/>
-    </row>
-    <row r="174" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
@@ -15284,10 +14997,8 @@
       <c r="AR174" s="8"/>
       <c r="AS174" s="8"/>
       <c r="AT174" s="8"/>
-      <c r="AU174" s="8"/>
-      <c r="AV174" s="8"/>
-    </row>
-    <row r="175" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
@@ -15334,10 +15045,8 @@
       <c r="AR175" s="8"/>
       <c r="AS175" s="8"/>
       <c r="AT175" s="8"/>
-      <c r="AU175" s="8"/>
-      <c r="AV175" s="8"/>
-    </row>
-    <row r="176" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
@@ -15384,10 +15093,8 @@
       <c r="AR176" s="8"/>
       <c r="AS176" s="8"/>
       <c r="AT176" s="8"/>
-      <c r="AU176" s="8"/>
-      <c r="AV176" s="8"/>
-    </row>
-    <row r="177" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
@@ -15434,10 +15141,8 @@
       <c r="AR177" s="8"/>
       <c r="AS177" s="8"/>
       <c r="AT177" s="8"/>
-      <c r="AU177" s="8"/>
-      <c r="AV177" s="8"/>
-    </row>
-    <row r="178" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
@@ -15484,10 +15189,8 @@
       <c r="AR178" s="8"/>
       <c r="AS178" s="8"/>
       <c r="AT178" s="8"/>
-      <c r="AU178" s="8"/>
-      <c r="AV178" s="8"/>
-    </row>
-    <row r="179" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
@@ -15534,10 +15237,8 @@
       <c r="AR179" s="8"/>
       <c r="AS179" s="8"/>
       <c r="AT179" s="8"/>
-      <c r="AU179" s="8"/>
-      <c r="AV179" s="8"/>
-    </row>
-    <row r="180" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
@@ -15584,10 +15285,8 @@
       <c r="AR180" s="8"/>
       <c r="AS180" s="8"/>
       <c r="AT180" s="8"/>
-      <c r="AU180" s="8"/>
-      <c r="AV180" s="8"/>
-    </row>
-    <row r="181" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
@@ -15634,10 +15333,8 @@
       <c r="AR181" s="8"/>
       <c r="AS181" s="8"/>
       <c r="AT181" s="8"/>
-      <c r="AU181" s="8"/>
-      <c r="AV181" s="8"/>
-    </row>
-    <row r="182" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
@@ -15684,10 +15381,8 @@
       <c r="AR182" s="8"/>
       <c r="AS182" s="8"/>
       <c r="AT182" s="8"/>
-      <c r="AU182" s="8"/>
-      <c r="AV182" s="8"/>
-    </row>
-    <row r="183" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
@@ -15734,10 +15429,8 @@
       <c r="AR183" s="8"/>
       <c r="AS183" s="8"/>
       <c r="AT183" s="8"/>
-      <c r="AU183" s="8"/>
-      <c r="AV183" s="8"/>
-    </row>
-    <row r="184" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A184" s="8"/>
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
@@ -15784,10 +15477,8 @@
       <c r="AR184" s="8"/>
       <c r="AS184" s="8"/>
       <c r="AT184" s="8"/>
-      <c r="AU184" s="8"/>
-      <c r="AV184" s="8"/>
-    </row>
-    <row r="185" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
@@ -15834,10 +15525,8 @@
       <c r="AR185" s="8"/>
       <c r="AS185" s="8"/>
       <c r="AT185" s="8"/>
-      <c r="AU185" s="8"/>
-      <c r="AV185" s="8"/>
-    </row>
-    <row r="186" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
@@ -15884,10 +15573,8 @@
       <c r="AR186" s="8"/>
       <c r="AS186" s="8"/>
       <c r="AT186" s="8"/>
-      <c r="AU186" s="8"/>
-      <c r="AV186" s="8"/>
-    </row>
-    <row r="187" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
@@ -15934,10 +15621,8 @@
       <c r="AR187" s="8"/>
       <c r="AS187" s="8"/>
       <c r="AT187" s="8"/>
-      <c r="AU187" s="8"/>
-      <c r="AV187" s="8"/>
-    </row>
-    <row r="188" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A188" s="8"/>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
@@ -15984,10 +15669,8 @@
       <c r="AR188" s="8"/>
       <c r="AS188" s="8"/>
       <c r="AT188" s="8"/>
-      <c r="AU188" s="8"/>
-      <c r="AV188" s="8"/>
-    </row>
-    <row r="189" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
@@ -16034,10 +15717,8 @@
       <c r="AR189" s="8"/>
       <c r="AS189" s="8"/>
       <c r="AT189" s="8"/>
-      <c r="AU189" s="8"/>
-      <c r="AV189" s="8"/>
-    </row>
-    <row r="190" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -16084,10 +15765,8 @@
       <c r="AR190" s="8"/>
       <c r="AS190" s="8"/>
       <c r="AT190" s="8"/>
-      <c r="AU190" s="8"/>
-      <c r="AV190" s="8"/>
-    </row>
-    <row r="191" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
@@ -16134,10 +15813,8 @@
       <c r="AR191" s="8"/>
       <c r="AS191" s="8"/>
       <c r="AT191" s="8"/>
-      <c r="AU191" s="8"/>
-      <c r="AV191" s="8"/>
-    </row>
-    <row r="192" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -16184,10 +15861,8 @@
       <c r="AR192" s="8"/>
       <c r="AS192" s="8"/>
       <c r="AT192" s="8"/>
-      <c r="AU192" s="8"/>
-      <c r="AV192" s="8"/>
-    </row>
-    <row r="193" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -16234,10 +15909,8 @@
       <c r="AR193" s="8"/>
       <c r="AS193" s="8"/>
       <c r="AT193" s="8"/>
-      <c r="AU193" s="8"/>
-      <c r="AV193" s="8"/>
-    </row>
-    <row r="194" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -16284,10 +15957,8 @@
       <c r="AR194" s="8"/>
       <c r="AS194" s="8"/>
       <c r="AT194" s="8"/>
-      <c r="AU194" s="8"/>
-      <c r="AV194" s="8"/>
-    </row>
-    <row r="195" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -16334,10 +16005,8 @@
       <c r="AR195" s="8"/>
       <c r="AS195" s="8"/>
       <c r="AT195" s="8"/>
-      <c r="AU195" s="8"/>
-      <c r="AV195" s="8"/>
-    </row>
-    <row r="196" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A196" s="8"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -16384,10 +16053,8 @@
       <c r="AR196" s="8"/>
       <c r="AS196" s="8"/>
       <c r="AT196" s="8"/>
-      <c r="AU196" s="8"/>
-      <c r="AV196" s="8"/>
-    </row>
-    <row r="197" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -16434,10 +16101,8 @@
       <c r="AR197" s="8"/>
       <c r="AS197" s="8"/>
       <c r="AT197" s="8"/>
-      <c r="AU197" s="8"/>
-      <c r="AV197" s="8"/>
-    </row>
-    <row r="198" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A198" s="8"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -16484,10 +16149,8 @@
       <c r="AR198" s="8"/>
       <c r="AS198" s="8"/>
       <c r="AT198" s="8"/>
-      <c r="AU198" s="8"/>
-      <c r="AV198" s="8"/>
-    </row>
-    <row r="199" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A199" s="8"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -16534,10 +16197,8 @@
       <c r="AR199" s="8"/>
       <c r="AS199" s="8"/>
       <c r="AT199" s="8"/>
-      <c r="AU199" s="8"/>
-      <c r="AV199" s="8"/>
-    </row>
-    <row r="200" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A200" s="8"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -16584,10 +16245,8 @@
       <c r="AR200" s="8"/>
       <c r="AS200" s="8"/>
       <c r="AT200" s="8"/>
-      <c r="AU200" s="8"/>
-      <c r="AV200" s="8"/>
-    </row>
-    <row r="201" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -16634,10 +16293,8 @@
       <c r="AR201" s="8"/>
       <c r="AS201" s="8"/>
       <c r="AT201" s="8"/>
-      <c r="AU201" s="8"/>
-      <c r="AV201" s="8"/>
-    </row>
-    <row r="202" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A202" s="8"/>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -16684,10 +16341,8 @@
       <c r="AR202" s="8"/>
       <c r="AS202" s="8"/>
       <c r="AT202" s="8"/>
-      <c r="AU202" s="8"/>
-      <c r="AV202" s="8"/>
-    </row>
-    <row r="203" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A203" s="8"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -16734,10 +16389,8 @@
       <c r="AR203" s="8"/>
       <c r="AS203" s="8"/>
       <c r="AT203" s="8"/>
-      <c r="AU203" s="8"/>
-      <c r="AV203" s="8"/>
-    </row>
-    <row r="204" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A204" s="8"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -16784,10 +16437,8 @@
       <c r="AR204" s="8"/>
       <c r="AS204" s="8"/>
       <c r="AT204" s="8"/>
-      <c r="AU204" s="8"/>
-      <c r="AV204" s="8"/>
-    </row>
-    <row r="205" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A205" s="8"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -16834,10 +16485,8 @@
       <c r="AR205" s="8"/>
       <c r="AS205" s="8"/>
       <c r="AT205" s="8"/>
-      <c r="AU205" s="8"/>
-      <c r="AV205" s="8"/>
-    </row>
-    <row r="206" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A206" s="8"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -16884,10 +16533,8 @@
       <c r="AR206" s="8"/>
       <c r="AS206" s="8"/>
       <c r="AT206" s="8"/>
-      <c r="AU206" s="8"/>
-      <c r="AV206" s="8"/>
-    </row>
-    <row r="207" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -16934,10 +16581,8 @@
       <c r="AR207" s="8"/>
       <c r="AS207" s="8"/>
       <c r="AT207" s="8"/>
-      <c r="AU207" s="8"/>
-      <c r="AV207" s="8"/>
-    </row>
-    <row r="208" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -16984,10 +16629,8 @@
       <c r="AR208" s="8"/>
       <c r="AS208" s="8"/>
       <c r="AT208" s="8"/>
-      <c r="AU208" s="8"/>
-      <c r="AV208" s="8"/>
-    </row>
-    <row r="209" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -17034,10 +16677,8 @@
       <c r="AR209" s="8"/>
       <c r="AS209" s="8"/>
       <c r="AT209" s="8"/>
-      <c r="AU209" s="8"/>
-      <c r="AV209" s="8"/>
-    </row>
-    <row r="210" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -17084,10 +16725,8 @@
       <c r="AR210" s="8"/>
       <c r="AS210" s="8"/>
       <c r="AT210" s="8"/>
-      <c r="AU210" s="8"/>
-      <c r="AV210" s="8"/>
-    </row>
-    <row r="211" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A211" s="8"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -17134,10 +16773,8 @@
       <c r="AR211" s="8"/>
       <c r="AS211" s="8"/>
       <c r="AT211" s="8"/>
-      <c r="AU211" s="8"/>
-      <c r="AV211" s="8"/>
-    </row>
-    <row r="212" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A212" s="8"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -17184,10 +16821,8 @@
       <c r="AR212" s="8"/>
       <c r="AS212" s="8"/>
       <c r="AT212" s="8"/>
-      <c r="AU212" s="8"/>
-      <c r="AV212" s="8"/>
-    </row>
-    <row r="213" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A213" s="8"/>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -17234,10 +16869,8 @@
       <c r="AR213" s="8"/>
       <c r="AS213" s="8"/>
       <c r="AT213" s="8"/>
-      <c r="AU213" s="8"/>
-      <c r="AV213" s="8"/>
-    </row>
-    <row r="214" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A214" s="8"/>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -17284,10 +16917,8 @@
       <c r="AR214" s="8"/>
       <c r="AS214" s="8"/>
       <c r="AT214" s="8"/>
-      <c r="AU214" s="8"/>
-      <c r="AV214" s="8"/>
-    </row>
-    <row r="215" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A215" s="8"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -17334,10 +16965,8 @@
       <c r="AR215" s="8"/>
       <c r="AS215" s="8"/>
       <c r="AT215" s="8"/>
-      <c r="AU215" s="8"/>
-      <c r="AV215" s="8"/>
-    </row>
-    <row r="216" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A216" s="8"/>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -17384,10 +17013,8 @@
       <c r="AR216" s="8"/>
       <c r="AS216" s="8"/>
       <c r="AT216" s="8"/>
-      <c r="AU216" s="8"/>
-      <c r="AV216" s="8"/>
-    </row>
-    <row r="217" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A217" s="8"/>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -17434,10 +17061,8 @@
       <c r="AR217" s="8"/>
       <c r="AS217" s="8"/>
       <c r="AT217" s="8"/>
-      <c r="AU217" s="8"/>
-      <c r="AV217" s="8"/>
-    </row>
-    <row r="218" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A218" s="8"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -17484,10 +17109,8 @@
       <c r="AR218" s="8"/>
       <c r="AS218" s="8"/>
       <c r="AT218" s="8"/>
-      <c r="AU218" s="8"/>
-      <c r="AV218" s="8"/>
-    </row>
-    <row r="219" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A219" s="8"/>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -17534,10 +17157,8 @@
       <c r="AR219" s="8"/>
       <c r="AS219" s="8"/>
       <c r="AT219" s="8"/>
-      <c r="AU219" s="8"/>
-      <c r="AV219" s="8"/>
-    </row>
-    <row r="220" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A220" s="8"/>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -17584,10 +17205,8 @@
       <c r="AR220" s="8"/>
       <c r="AS220" s="8"/>
       <c r="AT220" s="8"/>
-      <c r="AU220" s="8"/>
-      <c r="AV220" s="8"/>
-    </row>
-    <row r="221" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A221" s="8"/>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -17634,10 +17253,8 @@
       <c r="AR221" s="8"/>
       <c r="AS221" s="8"/>
       <c r="AT221" s="8"/>
-      <c r="AU221" s="8"/>
-      <c r="AV221" s="8"/>
-    </row>
-    <row r="222" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A222" s="8"/>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -17684,10 +17301,8 @@
       <c r="AR222" s="8"/>
       <c r="AS222" s="8"/>
       <c r="AT222" s="8"/>
-      <c r="AU222" s="8"/>
-      <c r="AV222" s="8"/>
-    </row>
-    <row r="223" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A223" s="8"/>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -17734,10 +17349,8 @@
       <c r="AR223" s="8"/>
       <c r="AS223" s="8"/>
       <c r="AT223" s="8"/>
-      <c r="AU223" s="8"/>
-      <c r="AV223" s="8"/>
-    </row>
-    <row r="224" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A224" s="8"/>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -17784,10 +17397,8 @@
       <c r="AR224" s="8"/>
       <c r="AS224" s="8"/>
       <c r="AT224" s="8"/>
-      <c r="AU224" s="8"/>
-      <c r="AV224" s="8"/>
-    </row>
-    <row r="225" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A225" s="8"/>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -17834,10 +17445,8 @@
       <c r="AR225" s="8"/>
       <c r="AS225" s="8"/>
       <c r="AT225" s="8"/>
-      <c r="AU225" s="8"/>
-      <c r="AV225" s="8"/>
-    </row>
-    <row r="226" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A226" s="8"/>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -17884,10 +17493,8 @@
       <c r="AR226" s="8"/>
       <c r="AS226" s="8"/>
       <c r="AT226" s="8"/>
-      <c r="AU226" s="8"/>
-      <c r="AV226" s="8"/>
-    </row>
-    <row r="227" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A227" s="8"/>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -17934,10 +17541,8 @@
       <c r="AR227" s="8"/>
       <c r="AS227" s="8"/>
       <c r="AT227" s="8"/>
-      <c r="AU227" s="8"/>
-      <c r="AV227" s="8"/>
-    </row>
-    <row r="228" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A228" s="8"/>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -17984,10 +17589,8 @@
       <c r="AR228" s="8"/>
       <c r="AS228" s="8"/>
       <c r="AT228" s="8"/>
-      <c r="AU228" s="8"/>
-      <c r="AV228" s="8"/>
-    </row>
-    <row r="229" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A229" s="8"/>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -18034,10 +17637,8 @@
       <c r="AR229" s="8"/>
       <c r="AS229" s="8"/>
       <c r="AT229" s="8"/>
-      <c r="AU229" s="8"/>
-      <c r="AV229" s="8"/>
-    </row>
-    <row r="230" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A230" s="8"/>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -18084,10 +17685,8 @@
       <c r="AR230" s="8"/>
       <c r="AS230" s="8"/>
       <c r="AT230" s="8"/>
-      <c r="AU230" s="8"/>
-      <c r="AV230" s="8"/>
-    </row>
-    <row r="231" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A231" s="8"/>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -18134,10 +17733,8 @@
       <c r="AR231" s="8"/>
       <c r="AS231" s="8"/>
       <c r="AT231" s="8"/>
-      <c r="AU231" s="8"/>
-      <c r="AV231" s="8"/>
-    </row>
-    <row r="232" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A232" s="8"/>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -18184,10 +17781,8 @@
       <c r="AR232" s="8"/>
       <c r="AS232" s="8"/>
       <c r="AT232" s="8"/>
-      <c r="AU232" s="8"/>
-      <c r="AV232" s="8"/>
-    </row>
-    <row r="233" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A233" s="8"/>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -18234,10 +17829,8 @@
       <c r="AR233" s="8"/>
       <c r="AS233" s="8"/>
       <c r="AT233" s="8"/>
-      <c r="AU233" s="8"/>
-      <c r="AV233" s="8"/>
-    </row>
-    <row r="234" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A234" s="8"/>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
@@ -18284,10 +17877,8 @@
       <c r="AR234" s="8"/>
       <c r="AS234" s="8"/>
       <c r="AT234" s="8"/>
-      <c r="AU234" s="8"/>
-      <c r="AV234" s="8"/>
-    </row>
-    <row r="235" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A235" s="8"/>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -18334,10 +17925,8 @@
       <c r="AR235" s="8"/>
       <c r="AS235" s="8"/>
       <c r="AT235" s="8"/>
-      <c r="AU235" s="8"/>
-      <c r="AV235" s="8"/>
-    </row>
-    <row r="236" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A236" s="8"/>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -18384,10 +17973,8 @@
       <c r="AR236" s="8"/>
       <c r="AS236" s="8"/>
       <c r="AT236" s="8"/>
-      <c r="AU236" s="8"/>
-      <c r="AV236" s="8"/>
-    </row>
-    <row r="237" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A237" s="8"/>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -18434,10 +18021,8 @@
       <c r="AR237" s="8"/>
       <c r="AS237" s="8"/>
       <c r="AT237" s="8"/>
-      <c r="AU237" s="8"/>
-      <c r="AV237" s="8"/>
-    </row>
-    <row r="238" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A238" s="8"/>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -18484,10 +18069,8 @@
       <c r="AR238" s="8"/>
       <c r="AS238" s="8"/>
       <c r="AT238" s="8"/>
-      <c r="AU238" s="8"/>
-      <c r="AV238" s="8"/>
-    </row>
-    <row r="239" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A239" s="8"/>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -18534,10 +18117,8 @@
       <c r="AR239" s="8"/>
       <c r="AS239" s="8"/>
       <c r="AT239" s="8"/>
-      <c r="AU239" s="8"/>
-      <c r="AV239" s="8"/>
-    </row>
-    <row r="240" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A240" s="8"/>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -18584,10 +18165,8 @@
       <c r="AR240" s="8"/>
       <c r="AS240" s="8"/>
       <c r="AT240" s="8"/>
-      <c r="AU240" s="8"/>
-      <c r="AV240" s="8"/>
-    </row>
-    <row r="241" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A241" s="8"/>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -18634,10 +18213,8 @@
       <c r="AR241" s="8"/>
       <c r="AS241" s="8"/>
       <c r="AT241" s="8"/>
-      <c r="AU241" s="8"/>
-      <c r="AV241" s="8"/>
-    </row>
-    <row r="242" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A242" s="8"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -18684,10 +18261,8 @@
       <c r="AR242" s="8"/>
       <c r="AS242" s="8"/>
       <c r="AT242" s="8"/>
-      <c r="AU242" s="8"/>
-      <c r="AV242" s="8"/>
-    </row>
-    <row r="243" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -18734,10 +18309,8 @@
       <c r="AR243" s="8"/>
       <c r="AS243" s="8"/>
       <c r="AT243" s="8"/>
-      <c r="AU243" s="8"/>
-      <c r="AV243" s="8"/>
-    </row>
-    <row r="244" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -18784,10 +18357,8 @@
       <c r="AR244" s="8"/>
       <c r="AS244" s="8"/>
       <c r="AT244" s="8"/>
-      <c r="AU244" s="8"/>
-      <c r="AV244" s="8"/>
-    </row>
-    <row r="245" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -18834,10 +18405,8 @@
       <c r="AR245" s="8"/>
       <c r="AS245" s="8"/>
       <c r="AT245" s="8"/>
-      <c r="AU245" s="8"/>
-      <c r="AV245" s="8"/>
-    </row>
-    <row r="246" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -18884,10 +18453,8 @@
       <c r="AR246" s="8"/>
       <c r="AS246" s="8"/>
       <c r="AT246" s="8"/>
-      <c r="AU246" s="8"/>
-      <c r="AV246" s="8"/>
-    </row>
-    <row r="247" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -18934,10 +18501,8 @@
       <c r="AR247" s="8"/>
       <c r="AS247" s="8"/>
       <c r="AT247" s="8"/>
-      <c r="AU247" s="8"/>
-      <c r="AV247" s="8"/>
-    </row>
-    <row r="248" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A248" s="8"/>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -18984,10 +18549,8 @@
       <c r="AR248" s="8"/>
       <c r="AS248" s="8"/>
       <c r="AT248" s="8"/>
-      <c r="AU248" s="8"/>
-      <c r="AV248" s="8"/>
-    </row>
-    <row r="249" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A249" s="8"/>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -19034,10 +18597,8 @@
       <c r="AR249" s="8"/>
       <c r="AS249" s="8"/>
       <c r="AT249" s="8"/>
-      <c r="AU249" s="8"/>
-      <c r="AV249" s="8"/>
-    </row>
-    <row r="250" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A250" s="8"/>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -19084,10 +18645,8 @@
       <c r="AR250" s="8"/>
       <c r="AS250" s="8"/>
       <c r="AT250" s="8"/>
-      <c r="AU250" s="8"/>
-      <c r="AV250" s="8"/>
-    </row>
-    <row r="251" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A251" s="8"/>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -19134,10 +18693,8 @@
       <c r="AR251" s="8"/>
       <c r="AS251" s="8"/>
       <c r="AT251" s="8"/>
-      <c r="AU251" s="8"/>
-      <c r="AV251" s="8"/>
-    </row>
-    <row r="252" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A252" s="8"/>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -19184,10 +18741,8 @@
       <c r="AR252" s="8"/>
       <c r="AS252" s="8"/>
       <c r="AT252" s="8"/>
-      <c r="AU252" s="8"/>
-      <c r="AV252" s="8"/>
-    </row>
-    <row r="253" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A253" s="8"/>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -19234,10 +18789,8 @@
       <c r="AR253" s="8"/>
       <c r="AS253" s="8"/>
       <c r="AT253" s="8"/>
-      <c r="AU253" s="8"/>
-      <c r="AV253" s="8"/>
-    </row>
-    <row r="254" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A254" s="8"/>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -19284,10 +18837,8 @@
       <c r="AR254" s="8"/>
       <c r="AS254" s="8"/>
       <c r="AT254" s="8"/>
-      <c r="AU254" s="8"/>
-      <c r="AV254" s="8"/>
-    </row>
-    <row r="255" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A255" s="8"/>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -19334,10 +18885,8 @@
       <c r="AR255" s="8"/>
       <c r="AS255" s="8"/>
       <c r="AT255" s="8"/>
-      <c r="AU255" s="8"/>
-      <c r="AV255" s="8"/>
-    </row>
-    <row r="256" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A256" s="8"/>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -19384,10 +18933,8 @@
       <c r="AR256" s="8"/>
       <c r="AS256" s="8"/>
       <c r="AT256" s="8"/>
-      <c r="AU256" s="8"/>
-      <c r="AV256" s="8"/>
-    </row>
-    <row r="257" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A257" s="8"/>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -19434,10 +18981,8 @@
       <c r="AR257" s="8"/>
       <c r="AS257" s="8"/>
       <c r="AT257" s="8"/>
-      <c r="AU257" s="8"/>
-      <c r="AV257" s="8"/>
-    </row>
-    <row r="258" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A258" s="8"/>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -19484,10 +19029,8 @@
       <c r="AR258" s="8"/>
       <c r="AS258" s="8"/>
       <c r="AT258" s="8"/>
-      <c r="AU258" s="8"/>
-      <c r="AV258" s="8"/>
-    </row>
-    <row r="259" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A259" s="8"/>
       <c r="B259" s="8"/>
       <c r="C259" s="8"/>
@@ -19534,10 +19077,8 @@
       <c r="AR259" s="8"/>
       <c r="AS259" s="8"/>
       <c r="AT259" s="8"/>
-      <c r="AU259" s="8"/>
-      <c r="AV259" s="8"/>
-    </row>
-    <row r="260" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A260" s="8"/>
       <c r="B260" s="8"/>
       <c r="C260" s="8"/>
@@ -19584,10 +19125,8 @@
       <c r="AR260" s="8"/>
       <c r="AS260" s="8"/>
       <c r="AT260" s="8"/>
-      <c r="AU260" s="8"/>
-      <c r="AV260" s="8"/>
-    </row>
-    <row r="261" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A261" s="8"/>
       <c r="B261" s="8"/>
       <c r="C261" s="8"/>
@@ -19634,10 +19173,8 @@
       <c r="AR261" s="8"/>
       <c r="AS261" s="8"/>
       <c r="AT261" s="8"/>
-      <c r="AU261" s="8"/>
-      <c r="AV261" s="8"/>
-    </row>
-    <row r="262" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A262" s="8"/>
       <c r="B262" s="8"/>
       <c r="C262" s="8"/>
@@ -19684,10 +19221,8 @@
       <c r="AR262" s="8"/>
       <c r="AS262" s="8"/>
       <c r="AT262" s="8"/>
-      <c r="AU262" s="8"/>
-      <c r="AV262" s="8"/>
-    </row>
-    <row r="263" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A263" s="8"/>
       <c r="B263" s="8"/>
       <c r="C263" s="8"/>
@@ -19734,10 +19269,8 @@
       <c r="AR263" s="8"/>
       <c r="AS263" s="8"/>
       <c r="AT263" s="8"/>
-      <c r="AU263" s="8"/>
-      <c r="AV263" s="8"/>
-    </row>
-    <row r="264" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A264" s="8"/>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
@@ -19784,10 +19317,8 @@
       <c r="AR264" s="8"/>
       <c r="AS264" s="8"/>
       <c r="AT264" s="8"/>
-      <c r="AU264" s="8"/>
-      <c r="AV264" s="8"/>
-    </row>
-    <row r="265" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A265" s="8"/>
       <c r="B265" s="8"/>
       <c r="C265" s="8"/>
@@ -19834,10 +19365,8 @@
       <c r="AR265" s="8"/>
       <c r="AS265" s="8"/>
       <c r="AT265" s="8"/>
-      <c r="AU265" s="8"/>
-      <c r="AV265" s="8"/>
-    </row>
-    <row r="266" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A266" s="8"/>
       <c r="B266" s="8"/>
       <c r="C266" s="8"/>
@@ -19884,10 +19413,8 @@
       <c r="AR266" s="8"/>
       <c r="AS266" s="8"/>
       <c r="AT266" s="8"/>
-      <c r="AU266" s="8"/>
-      <c r="AV266" s="8"/>
-    </row>
-    <row r="267" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A267" s="8"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8"/>
@@ -19934,10 +19461,8 @@
       <c r="AR267" s="8"/>
       <c r="AS267" s="8"/>
       <c r="AT267" s="8"/>
-      <c r="AU267" s="8"/>
-      <c r="AV267" s="8"/>
-    </row>
-    <row r="268" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A268" s="8"/>
       <c r="B268" s="8"/>
       <c r="C268" s="8"/>
@@ -19984,10 +19509,8 @@
       <c r="AR268" s="8"/>
       <c r="AS268" s="8"/>
       <c r="AT268" s="8"/>
-      <c r="AU268" s="8"/>
-      <c r="AV268" s="8"/>
-    </row>
-    <row r="269" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A269" s="8"/>
       <c r="B269" s="8"/>
       <c r="C269" s="8"/>
@@ -20034,10 +19557,8 @@
       <c r="AR269" s="8"/>
       <c r="AS269" s="8"/>
       <c r="AT269" s="8"/>
-      <c r="AU269" s="8"/>
-      <c r="AV269" s="8"/>
-    </row>
-    <row r="270" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A270" s="8"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
@@ -20084,10 +19605,8 @@
       <c r="AR270" s="8"/>
       <c r="AS270" s="8"/>
       <c r="AT270" s="8"/>
-      <c r="AU270" s="8"/>
-      <c r="AV270" s="8"/>
-    </row>
-    <row r="271" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A271" s="8"/>
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
@@ -20134,10 +19653,8 @@
       <c r="AR271" s="8"/>
       <c r="AS271" s="8"/>
       <c r="AT271" s="8"/>
-      <c r="AU271" s="8"/>
-      <c r="AV271" s="8"/>
-    </row>
-    <row r="272" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A272" s="8"/>
       <c r="B272" s="8"/>
       <c r="C272" s="8"/>
@@ -20184,10 +19701,8 @@
       <c r="AR272" s="8"/>
       <c r="AS272" s="8"/>
       <c r="AT272" s="8"/>
-      <c r="AU272" s="8"/>
-      <c r="AV272" s="8"/>
-    </row>
-    <row r="273" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -20234,10 +19749,8 @@
       <c r="AR273" s="8"/>
       <c r="AS273" s="8"/>
       <c r="AT273" s="8"/>
-      <c r="AU273" s="8"/>
-      <c r="AV273" s="8"/>
-    </row>
-    <row r="274" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A274" s="8"/>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
@@ -20284,10 +19797,8 @@
       <c r="AR274" s="8"/>
       <c r="AS274" s="8"/>
       <c r="AT274" s="8"/>
-      <c r="AU274" s="8"/>
-      <c r="AV274" s="8"/>
-    </row>
-    <row r="275" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A275" s="8"/>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
@@ -20334,10 +19845,8 @@
       <c r="AR275" s="8"/>
       <c r="AS275" s="8"/>
       <c r="AT275" s="8"/>
-      <c r="AU275" s="8"/>
-      <c r="AV275" s="8"/>
-    </row>
-    <row r="276" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A276" s="8"/>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -20384,10 +19893,8 @@
       <c r="AR276" s="8"/>
       <c r="AS276" s="8"/>
       <c r="AT276" s="8"/>
-      <c r="AU276" s="8"/>
-      <c r="AV276" s="8"/>
-    </row>
-    <row r="277" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A277" s="8"/>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -20434,10 +19941,8 @@
       <c r="AR277" s="8"/>
       <c r="AS277" s="8"/>
       <c r="AT277" s="8"/>
-      <c r="AU277" s="8"/>
-      <c r="AV277" s="8"/>
-    </row>
-    <row r="278" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A278" s="8"/>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -20484,10 +19989,8 @@
       <c r="AR278" s="8"/>
       <c r="AS278" s="8"/>
       <c r="AT278" s="8"/>
-      <c r="AU278" s="8"/>
-      <c r="AV278" s="8"/>
-    </row>
-    <row r="279" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A279" s="8"/>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -20534,10 +20037,8 @@
       <c r="AR279" s="8"/>
       <c r="AS279" s="8"/>
       <c r="AT279" s="8"/>
-      <c r="AU279" s="8"/>
-      <c r="AV279" s="8"/>
-    </row>
-    <row r="280" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A280" s="8"/>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -20584,10 +20085,8 @@
       <c r="AR280" s="8"/>
       <c r="AS280" s="8"/>
       <c r="AT280" s="8"/>
-      <c r="AU280" s="8"/>
-      <c r="AV280" s="8"/>
-    </row>
-    <row r="281" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A281" s="8"/>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -20634,10 +20133,8 @@
       <c r="AR281" s="8"/>
       <c r="AS281" s="8"/>
       <c r="AT281" s="8"/>
-      <c r="AU281" s="8"/>
-      <c r="AV281" s="8"/>
-    </row>
-    <row r="282" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A282" s="8"/>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -20684,10 +20181,8 @@
       <c r="AR282" s="8"/>
       <c r="AS282" s="8"/>
       <c r="AT282" s="8"/>
-      <c r="AU282" s="8"/>
-      <c r="AV282" s="8"/>
-    </row>
-    <row r="283" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A283" s="8"/>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -20734,10 +20229,8 @@
       <c r="AR283" s="8"/>
       <c r="AS283" s="8"/>
       <c r="AT283" s="8"/>
-      <c r="AU283" s="8"/>
-      <c r="AV283" s="8"/>
-    </row>
-    <row r="284" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A284" s="8"/>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -20784,10 +20277,8 @@
       <c r="AR284" s="8"/>
       <c r="AS284" s="8"/>
       <c r="AT284" s="8"/>
-      <c r="AU284" s="8"/>
-      <c r="AV284" s="8"/>
-    </row>
-    <row r="285" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A285" s="8"/>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -20834,10 +20325,8 @@
       <c r="AR285" s="8"/>
       <c r="AS285" s="8"/>
       <c r="AT285" s="8"/>
-      <c r="AU285" s="8"/>
-      <c r="AV285" s="8"/>
-    </row>
-    <row r="286" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A286" s="8"/>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -20884,10 +20373,8 @@
       <c r="AR286" s="8"/>
       <c r="AS286" s="8"/>
       <c r="AT286" s="8"/>
-      <c r="AU286" s="8"/>
-      <c r="AV286" s="8"/>
-    </row>
-    <row r="287" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A287" s="8"/>
       <c r="B287" s="8"/>
       <c r="C287" s="8"/>
@@ -20934,10 +20421,8 @@
       <c r="AR287" s="8"/>
       <c r="AS287" s="8"/>
       <c r="AT287" s="8"/>
-      <c r="AU287" s="8"/>
-      <c r="AV287" s="8"/>
-    </row>
-    <row r="288" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A288" s="8"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8"/>
@@ -20984,10 +20469,8 @@
       <c r="AR288" s="8"/>
       <c r="AS288" s="8"/>
       <c r="AT288" s="8"/>
-      <c r="AU288" s="8"/>
-      <c r="AV288" s="8"/>
-    </row>
-    <row r="289" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8"/>
@@ -21034,10 +20517,8 @@
       <c r="AR289" s="8"/>
       <c r="AS289" s="8"/>
       <c r="AT289" s="8"/>
-      <c r="AU289" s="8"/>
-      <c r="AV289" s="8"/>
-    </row>
-    <row r="290" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8"/>
@@ -21084,10 +20565,8 @@
       <c r="AR290" s="8"/>
       <c r="AS290" s="8"/>
       <c r="AT290" s="8"/>
-      <c r="AU290" s="8"/>
-      <c r="AV290" s="8"/>
-    </row>
-    <row r="291" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8"/>
@@ -21134,10 +20613,8 @@
       <c r="AR291" s="8"/>
       <c r="AS291" s="8"/>
       <c r="AT291" s="8"/>
-      <c r="AU291" s="8"/>
-      <c r="AV291" s="8"/>
-    </row>
-    <row r="292" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8"/>
@@ -21184,10 +20661,8 @@
       <c r="AR292" s="8"/>
       <c r="AS292" s="8"/>
       <c r="AT292" s="8"/>
-      <c r="AU292" s="8"/>
-      <c r="AV292" s="8"/>
-    </row>
-    <row r="293" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A293" s="8"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
@@ -21234,10 +20709,8 @@
       <c r="AR293" s="8"/>
       <c r="AS293" s="8"/>
       <c r="AT293" s="8"/>
-      <c r="AU293" s="8"/>
-      <c r="AV293" s="8"/>
-    </row>
-    <row r="294" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A294" s="8"/>
       <c r="B294" s="8"/>
       <c r="C294" s="8"/>
@@ -21284,10 +20757,8 @@
       <c r="AR294" s="8"/>
       <c r="AS294" s="8"/>
       <c r="AT294" s="8"/>
-      <c r="AU294" s="8"/>
-      <c r="AV294" s="8"/>
-    </row>
-    <row r="295" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A295" s="8"/>
       <c r="B295" s="8"/>
       <c r="C295" s="8"/>
@@ -21334,10 +20805,8 @@
       <c r="AR295" s="8"/>
       <c r="AS295" s="8"/>
       <c r="AT295" s="8"/>
-      <c r="AU295" s="8"/>
-      <c r="AV295" s="8"/>
-    </row>
-    <row r="296" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A296" s="8"/>
       <c r="B296" s="8"/>
       <c r="C296" s="8"/>
@@ -21384,10 +20853,8 @@
       <c r="AR296" s="8"/>
       <c r="AS296" s="8"/>
       <c r="AT296" s="8"/>
-      <c r="AU296" s="8"/>
-      <c r="AV296" s="8"/>
-    </row>
-    <row r="297" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A297" s="8"/>
       <c r="B297" s="8"/>
       <c r="C297" s="8"/>
@@ -21434,10 +20901,8 @@
       <c r="AR297" s="8"/>
       <c r="AS297" s="8"/>
       <c r="AT297" s="8"/>
-      <c r="AU297" s="8"/>
-      <c r="AV297" s="8"/>
-    </row>
-    <row r="298" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A298" s="8"/>
       <c r="B298" s="8"/>
       <c r="C298" s="8"/>
@@ -21484,10 +20949,8 @@
       <c r="AR298" s="8"/>
       <c r="AS298" s="8"/>
       <c r="AT298" s="8"/>
-      <c r="AU298" s="8"/>
-      <c r="AV298" s="8"/>
-    </row>
-    <row r="299" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A299" s="8"/>
       <c r="B299" s="8"/>
       <c r="C299" s="8"/>
@@ -21534,10 +20997,8 @@
       <c r="AR299" s="8"/>
       <c r="AS299" s="8"/>
       <c r="AT299" s="8"/>
-      <c r="AU299" s="8"/>
-      <c r="AV299" s="8"/>
-    </row>
-    <row r="300" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A300" s="8"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
@@ -21584,10 +21045,8 @@
       <c r="AR300" s="8"/>
       <c r="AS300" s="8"/>
       <c r="AT300" s="8"/>
-      <c r="AU300" s="8"/>
-      <c r="AV300" s="8"/>
-    </row>
-    <row r="301" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A301" s="8"/>
       <c r="B301" s="8"/>
       <c r="C301" s="8"/>
@@ -21634,10 +21093,8 @@
       <c r="AR301" s="8"/>
       <c r="AS301" s="8"/>
       <c r="AT301" s="8"/>
-      <c r="AU301" s="8"/>
-      <c r="AV301" s="8"/>
-    </row>
-    <row r="302" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A302" s="8"/>
       <c r="B302" s="8"/>
       <c r="C302" s="8"/>
@@ -21684,10 +21141,8 @@
       <c r="AR302" s="8"/>
       <c r="AS302" s="8"/>
       <c r="AT302" s="8"/>
-      <c r="AU302" s="8"/>
-      <c r="AV302" s="8"/>
-    </row>
-    <row r="303" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A303" s="8"/>
       <c r="B303" s="8"/>
       <c r="C303" s="8"/>
@@ -21734,10 +21189,8 @@
       <c r="AR303" s="8"/>
       <c r="AS303" s="8"/>
       <c r="AT303" s="8"/>
-      <c r="AU303" s="8"/>
-      <c r="AV303" s="8"/>
-    </row>
-    <row r="304" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A304" s="8"/>
       <c r="B304" s="8"/>
       <c r="C304" s="8"/>
@@ -21784,10 +21237,8 @@
       <c r="AR304" s="8"/>
       <c r="AS304" s="8"/>
       <c r="AT304" s="8"/>
-      <c r="AU304" s="8"/>
-      <c r="AV304" s="8"/>
-    </row>
-    <row r="305" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A305" s="8"/>
       <c r="B305" s="8"/>
       <c r="C305" s="8"/>
@@ -21834,10 +21285,8 @@
       <c r="AR305" s="8"/>
       <c r="AS305" s="8"/>
       <c r="AT305" s="8"/>
-      <c r="AU305" s="8"/>
-      <c r="AV305" s="8"/>
-    </row>
-    <row r="306" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A306" s="8"/>
       <c r="B306" s="8"/>
       <c r="C306" s="8"/>
@@ -21884,10 +21333,8 @@
       <c r="AR306" s="8"/>
       <c r="AS306" s="8"/>
       <c r="AT306" s="8"/>
-      <c r="AU306" s="8"/>
-      <c r="AV306" s="8"/>
-    </row>
-    <row r="307" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A307" s="8"/>
       <c r="B307" s="8"/>
       <c r="C307" s="8"/>
@@ -21934,10 +21381,8 @@
       <c r="AR307" s="8"/>
       <c r="AS307" s="8"/>
       <c r="AT307" s="8"/>
-      <c r="AU307" s="8"/>
-      <c r="AV307" s="8"/>
-    </row>
-    <row r="308" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A308" s="8"/>
       <c r="B308" s="8"/>
       <c r="C308" s="8"/>
@@ -21984,10 +21429,8 @@
       <c r="AR308" s="8"/>
       <c r="AS308" s="8"/>
       <c r="AT308" s="8"/>
-      <c r="AU308" s="8"/>
-      <c r="AV308" s="8"/>
-    </row>
-    <row r="309" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A309" s="8"/>
       <c r="B309" s="8"/>
       <c r="C309" s="8"/>
@@ -22034,10 +21477,8 @@
       <c r="AR309" s="8"/>
       <c r="AS309" s="8"/>
       <c r="AT309" s="8"/>
-      <c r="AU309" s="8"/>
-      <c r="AV309" s="8"/>
-    </row>
-    <row r="310" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A310" s="8"/>
       <c r="B310" s="8"/>
       <c r="C310" s="8"/>
@@ -22084,10 +21525,8 @@
       <c r="AR310" s="8"/>
       <c r="AS310" s="8"/>
       <c r="AT310" s="8"/>
-      <c r="AU310" s="8"/>
-      <c r="AV310" s="8"/>
-    </row>
-    <row r="311" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A311" s="8"/>
       <c r="B311" s="8"/>
       <c r="C311" s="8"/>
@@ -22134,10 +21573,8 @@
       <c r="AR311" s="8"/>
       <c r="AS311" s="8"/>
       <c r="AT311" s="8"/>
-      <c r="AU311" s="8"/>
-      <c r="AV311" s="8"/>
-    </row>
-    <row r="312" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A312" s="8"/>
       <c r="B312" s="8"/>
       <c r="C312" s="8"/>
@@ -22184,10 +21621,8 @@
       <c r="AR312" s="8"/>
       <c r="AS312" s="8"/>
       <c r="AT312" s="8"/>
-      <c r="AU312" s="8"/>
-      <c r="AV312" s="8"/>
-    </row>
-    <row r="313" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A313" s="8"/>
       <c r="B313" s="8"/>
       <c r="C313" s="8"/>
@@ -22234,10 +21669,8 @@
       <c r="AR313" s="8"/>
       <c r="AS313" s="8"/>
       <c r="AT313" s="8"/>
-      <c r="AU313" s="8"/>
-      <c r="AV313" s="8"/>
-    </row>
-    <row r="314" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A314" s="8"/>
       <c r="B314" s="8"/>
       <c r="C314" s="8"/>
@@ -22284,10 +21717,8 @@
       <c r="AR314" s="8"/>
       <c r="AS314" s="8"/>
       <c r="AT314" s="8"/>
-      <c r="AU314" s="8"/>
-      <c r="AV314" s="8"/>
-    </row>
-    <row r="315" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A315" s="8"/>
       <c r="B315" s="8"/>
       <c r="C315" s="8"/>
@@ -22334,10 +21765,8 @@
       <c r="AR315" s="8"/>
       <c r="AS315" s="8"/>
       <c r="AT315" s="8"/>
-      <c r="AU315" s="8"/>
-      <c r="AV315" s="8"/>
-    </row>
-    <row r="316" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A316" s="8"/>
       <c r="B316" s="8"/>
       <c r="C316" s="8"/>
@@ -22384,10 +21813,8 @@
       <c r="AR316" s="8"/>
       <c r="AS316" s="8"/>
       <c r="AT316" s="8"/>
-      <c r="AU316" s="8"/>
-      <c r="AV316" s="8"/>
-    </row>
-    <row r="317" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A317" s="8"/>
       <c r="B317" s="8"/>
       <c r="C317" s="8"/>
@@ -22434,10 +21861,8 @@
       <c r="AR317" s="8"/>
       <c r="AS317" s="8"/>
       <c r="AT317" s="8"/>
-      <c r="AU317" s="8"/>
-      <c r="AV317" s="8"/>
-    </row>
-    <row r="318" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A318" s="8"/>
       <c r="B318" s="8"/>
       <c r="C318" s="8"/>
@@ -22484,10 +21909,8 @@
       <c r="AR318" s="8"/>
       <c r="AS318" s="8"/>
       <c r="AT318" s="8"/>
-      <c r="AU318" s="8"/>
-      <c r="AV318" s="8"/>
-    </row>
-    <row r="319" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A319" s="8"/>
       <c r="B319" s="8"/>
       <c r="C319" s="8"/>
@@ -22534,10 +21957,8 @@
       <c r="AR319" s="8"/>
       <c r="AS319" s="8"/>
       <c r="AT319" s="8"/>
-      <c r="AU319" s="8"/>
-      <c r="AV319" s="8"/>
-    </row>
-    <row r="320" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A320" s="8"/>
       <c r="B320" s="8"/>
       <c r="C320" s="8"/>
@@ -22584,10 +22005,8 @@
       <c r="AR320" s="8"/>
       <c r="AS320" s="8"/>
       <c r="AT320" s="8"/>
-      <c r="AU320" s="8"/>
-      <c r="AV320" s="8"/>
-    </row>
-    <row r="321" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A321" s="8"/>
       <c r="B321" s="8"/>
       <c r="C321" s="8"/>
@@ -22634,10 +22053,8 @@
       <c r="AR321" s="8"/>
       <c r="AS321" s="8"/>
       <c r="AT321" s="8"/>
-      <c r="AU321" s="8"/>
-      <c r="AV321" s="8"/>
-    </row>
-    <row r="322" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A322" s="8"/>
       <c r="B322" s="8"/>
       <c r="C322" s="8"/>
@@ -22684,10 +22101,8 @@
       <c r="AR322" s="8"/>
       <c r="AS322" s="8"/>
       <c r="AT322" s="8"/>
-      <c r="AU322" s="8"/>
-      <c r="AV322" s="8"/>
-    </row>
-    <row r="323" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A323" s="8"/>
       <c r="B323" s="8"/>
       <c r="C323" s="8"/>
@@ -22734,10 +22149,8 @@
       <c r="AR323" s="8"/>
       <c r="AS323" s="8"/>
       <c r="AT323" s="8"/>
-      <c r="AU323" s="8"/>
-      <c r="AV323" s="8"/>
-    </row>
-    <row r="324" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A324" s="8"/>
       <c r="B324" s="8"/>
       <c r="C324" s="8"/>
@@ -22784,10 +22197,8 @@
       <c r="AR324" s="8"/>
       <c r="AS324" s="8"/>
       <c r="AT324" s="8"/>
-      <c r="AU324" s="8"/>
-      <c r="AV324" s="8"/>
-    </row>
-    <row r="325" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A325" s="8"/>
       <c r="B325" s="8"/>
       <c r="C325" s="8"/>
@@ -22834,10 +22245,8 @@
       <c r="AR325" s="8"/>
       <c r="AS325" s="8"/>
       <c r="AT325" s="8"/>
-      <c r="AU325" s="8"/>
-      <c r="AV325" s="8"/>
-    </row>
-    <row r="326" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A326" s="8"/>
       <c r="B326" s="8"/>
       <c r="C326" s="8"/>
@@ -22884,10 +22293,8 @@
       <c r="AR326" s="8"/>
       <c r="AS326" s="8"/>
       <c r="AT326" s="8"/>
-      <c r="AU326" s="8"/>
-      <c r="AV326" s="8"/>
-    </row>
-    <row r="327" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A327" s="8"/>
       <c r="B327" s="8"/>
       <c r="C327" s="8"/>
@@ -22934,10 +22341,8 @@
       <c r="AR327" s="8"/>
       <c r="AS327" s="8"/>
       <c r="AT327" s="8"/>
-      <c r="AU327" s="8"/>
-      <c r="AV327" s="8"/>
-    </row>
-    <row r="328" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A328" s="8"/>
       <c r="B328" s="8"/>
       <c r="C328" s="8"/>
@@ -22984,10 +22389,8 @@
       <c r="AR328" s="8"/>
       <c r="AS328" s="8"/>
       <c r="AT328" s="8"/>
-      <c r="AU328" s="8"/>
-      <c r="AV328" s="8"/>
-    </row>
-    <row r="329" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A329" s="8"/>
       <c r="B329" s="8"/>
       <c r="C329" s="8"/>
@@ -23034,10 +22437,8 @@
       <c r="AR329" s="8"/>
       <c r="AS329" s="8"/>
       <c r="AT329" s="8"/>
-      <c r="AU329" s="8"/>
-      <c r="AV329" s="8"/>
-    </row>
-    <row r="330" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A330" s="8"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8"/>
@@ -23084,10 +22485,8 @@
       <c r="AR330" s="8"/>
       <c r="AS330" s="8"/>
       <c r="AT330" s="8"/>
-      <c r="AU330" s="8"/>
-      <c r="AV330" s="8"/>
-    </row>
-    <row r="331" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A331" s="8"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8"/>
@@ -23134,10 +22533,8 @@
       <c r="AR331" s="8"/>
       <c r="AS331" s="8"/>
       <c r="AT331" s="8"/>
-      <c r="AU331" s="8"/>
-      <c r="AV331" s="8"/>
-    </row>
-    <row r="332" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A332" s="8"/>
       <c r="B332" s="8"/>
       <c r="C332" s="8"/>
@@ -23184,10 +22581,8 @@
       <c r="AR332" s="8"/>
       <c r="AS332" s="8"/>
       <c r="AT332" s="8"/>
-      <c r="AU332" s="8"/>
-      <c r="AV332" s="8"/>
-    </row>
-    <row r="333" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A333" s="8"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
@@ -23234,10 +22629,8 @@
       <c r="AR333" s="8"/>
       <c r="AS333" s="8"/>
       <c r="AT333" s="8"/>
-      <c r="AU333" s="8"/>
-      <c r="AV333" s="8"/>
-    </row>
-    <row r="334" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A334" s="8"/>
       <c r="B334" s="8"/>
       <c r="C334" s="8"/>
@@ -23284,10 +22677,8 @@
       <c r="AR334" s="8"/>
       <c r="AS334" s="8"/>
       <c r="AT334" s="8"/>
-      <c r="AU334" s="8"/>
-      <c r="AV334" s="8"/>
-    </row>
-    <row r="335" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A335" s="8"/>
       <c r="B335" s="8"/>
       <c r="C335" s="8"/>
@@ -23334,10 +22725,8 @@
       <c r="AR335" s="8"/>
       <c r="AS335" s="8"/>
       <c r="AT335" s="8"/>
-      <c r="AU335" s="8"/>
-      <c r="AV335" s="8"/>
-    </row>
-    <row r="336" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A336" s="8"/>
       <c r="B336" s="8"/>
       <c r="C336" s="8"/>
@@ -23384,10 +22773,8 @@
       <c r="AR336" s="8"/>
       <c r="AS336" s="8"/>
       <c r="AT336" s="8"/>
-      <c r="AU336" s="8"/>
-      <c r="AV336" s="8"/>
-    </row>
-    <row r="337" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A337" s="8"/>
       <c r="B337" s="8"/>
       <c r="C337" s="8"/>
@@ -23434,10 +22821,8 @@
       <c r="AR337" s="8"/>
       <c r="AS337" s="8"/>
       <c r="AT337" s="8"/>
-      <c r="AU337" s="8"/>
-      <c r="AV337" s="8"/>
-    </row>
-    <row r="338" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A338" s="8"/>
       <c r="B338" s="8"/>
       <c r="C338" s="8"/>
@@ -23484,10 +22869,8 @@
       <c r="AR338" s="8"/>
       <c r="AS338" s="8"/>
       <c r="AT338" s="8"/>
-      <c r="AU338" s="8"/>
-      <c r="AV338" s="8"/>
-    </row>
-    <row r="339" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A339" s="8"/>
       <c r="B339" s="8"/>
       <c r="C339" s="8"/>
@@ -23534,10 +22917,8 @@
       <c r="AR339" s="8"/>
       <c r="AS339" s="8"/>
       <c r="AT339" s="8"/>
-      <c r="AU339" s="8"/>
-      <c r="AV339" s="8"/>
-    </row>
-    <row r="340" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A340" s="8"/>
       <c r="B340" s="8"/>
       <c r="C340" s="8"/>
@@ -23584,10 +22965,8 @@
       <c r="AR340" s="8"/>
       <c r="AS340" s="8"/>
       <c r="AT340" s="8"/>
-      <c r="AU340" s="8"/>
-      <c r="AV340" s="8"/>
-    </row>
-    <row r="341" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A341" s="8"/>
       <c r="B341" s="8"/>
       <c r="C341" s="8"/>
@@ -23634,10 +23013,8 @@
       <c r="AR341" s="8"/>
       <c r="AS341" s="8"/>
       <c r="AT341" s="8"/>
-      <c r="AU341" s="8"/>
-      <c r="AV341" s="8"/>
-    </row>
-    <row r="342" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A342" s="8"/>
       <c r="B342" s="8"/>
       <c r="C342" s="8"/>
@@ -23684,10 +23061,8 @@
       <c r="AR342" s="8"/>
       <c r="AS342" s="8"/>
       <c r="AT342" s="8"/>
-      <c r="AU342" s="8"/>
-      <c r="AV342" s="8"/>
-    </row>
-    <row r="343" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A343" s="8"/>
       <c r="B343" s="8"/>
       <c r="C343" s="8"/>
@@ -23734,10 +23109,8 @@
       <c r="AR343" s="8"/>
       <c r="AS343" s="8"/>
       <c r="AT343" s="8"/>
-      <c r="AU343" s="8"/>
-      <c r="AV343" s="8"/>
-    </row>
-    <row r="344" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A344" s="8"/>
       <c r="B344" s="8"/>
       <c r="C344" s="8"/>
@@ -23784,10 +23157,8 @@
       <c r="AR344" s="8"/>
       <c r="AS344" s="8"/>
       <c r="AT344" s="8"/>
-      <c r="AU344" s="8"/>
-      <c r="AV344" s="8"/>
-    </row>
-    <row r="345" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A345" s="8"/>
       <c r="B345" s="8"/>
       <c r="C345" s="8"/>
@@ -23834,10 +23205,8 @@
       <c r="AR345" s="8"/>
       <c r="AS345" s="8"/>
       <c r="AT345" s="8"/>
-      <c r="AU345" s="8"/>
-      <c r="AV345" s="8"/>
-    </row>
-    <row r="346" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A346" s="8"/>
       <c r="B346" s="8"/>
       <c r="C346" s="8"/>
@@ -23884,10 +23253,8 @@
       <c r="AR346" s="8"/>
       <c r="AS346" s="8"/>
       <c r="AT346" s="8"/>
-      <c r="AU346" s="8"/>
-      <c r="AV346" s="8"/>
-    </row>
-    <row r="347" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A347" s="8"/>
       <c r="B347" s="8"/>
       <c r="C347" s="8"/>
@@ -23934,10 +23301,8 @@
       <c r="AR347" s="8"/>
       <c r="AS347" s="8"/>
       <c r="AT347" s="8"/>
-      <c r="AU347" s="8"/>
-      <c r="AV347" s="8"/>
-    </row>
-    <row r="348" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A348" s="8"/>
       <c r="B348" s="8"/>
       <c r="C348" s="8"/>
@@ -23984,10 +23349,8 @@
       <c r="AR348" s="8"/>
       <c r="AS348" s="8"/>
       <c r="AT348" s="8"/>
-      <c r="AU348" s="8"/>
-      <c r="AV348" s="8"/>
-    </row>
-    <row r="349" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A349" s="8"/>
       <c r="B349" s="8"/>
       <c r="C349" s="8"/>
@@ -24034,10 +23397,8 @@
       <c r="AR349" s="8"/>
       <c r="AS349" s="8"/>
       <c r="AT349" s="8"/>
-      <c r="AU349" s="8"/>
-      <c r="AV349" s="8"/>
-    </row>
-    <row r="350" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A350" s="8"/>
       <c r="B350" s="8"/>
       <c r="C350" s="8"/>
@@ -24084,10 +23445,8 @@
       <c r="AR350" s="8"/>
       <c r="AS350" s="8"/>
       <c r="AT350" s="8"/>
-      <c r="AU350" s="8"/>
-      <c r="AV350" s="8"/>
-    </row>
-    <row r="351" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A351" s="8"/>
       <c r="B351" s="8"/>
       <c r="C351" s="8"/>
@@ -24134,10 +23493,8 @@
       <c r="AR351" s="8"/>
       <c r="AS351" s="8"/>
       <c r="AT351" s="8"/>
-      <c r="AU351" s="8"/>
-      <c r="AV351" s="8"/>
-    </row>
-    <row r="352" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A352" s="8"/>
       <c r="B352" s="8"/>
       <c r="C352" s="8"/>
@@ -24184,10 +23541,8 @@
       <c r="AR352" s="8"/>
       <c r="AS352" s="8"/>
       <c r="AT352" s="8"/>
-      <c r="AU352" s="8"/>
-      <c r="AV352" s="8"/>
-    </row>
-    <row r="353" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A353" s="8"/>
       <c r="B353" s="8"/>
       <c r="C353" s="8"/>
@@ -24234,10 +23589,8 @@
       <c r="AR353" s="8"/>
       <c r="AS353" s="8"/>
       <c r="AT353" s="8"/>
-      <c r="AU353" s="8"/>
-      <c r="AV353" s="8"/>
-    </row>
-    <row r="354" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A354" s="8"/>
       <c r="B354" s="8"/>
       <c r="C354" s="8"/>
@@ -24284,10 +23637,8 @@
       <c r="AR354" s="8"/>
       <c r="AS354" s="8"/>
       <c r="AT354" s="8"/>
-      <c r="AU354" s="8"/>
-      <c r="AV354" s="8"/>
-    </row>
-    <row r="355" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A355" s="8"/>
       <c r="B355" s="8"/>
       <c r="C355" s="8"/>
@@ -24334,10 +23685,8 @@
       <c r="AR355" s="8"/>
       <c r="AS355" s="8"/>
       <c r="AT355" s="8"/>
-      <c r="AU355" s="8"/>
-      <c r="AV355" s="8"/>
-    </row>
-    <row r="356" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A356" s="8"/>
       <c r="B356" s="8"/>
       <c r="C356" s="8"/>
@@ -24384,10 +23733,8 @@
       <c r="AR356" s="8"/>
       <c r="AS356" s="8"/>
       <c r="AT356" s="8"/>
-      <c r="AU356" s="8"/>
-      <c r="AV356" s="8"/>
-    </row>
-    <row r="357" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A357" s="8"/>
       <c r="B357" s="8"/>
       <c r="C357" s="8"/>
@@ -24434,10 +23781,8 @@
       <c r="AR357" s="8"/>
       <c r="AS357" s="8"/>
       <c r="AT357" s="8"/>
-      <c r="AU357" s="8"/>
-      <c r="AV357" s="8"/>
-    </row>
-    <row r="358" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A358" s="8"/>
       <c r="B358" s="8"/>
       <c r="C358" s="8"/>
@@ -24484,10 +23829,8 @@
       <c r="AR358" s="8"/>
       <c r="AS358" s="8"/>
       <c r="AT358" s="8"/>
-      <c r="AU358" s="8"/>
-      <c r="AV358" s="8"/>
-    </row>
-    <row r="359" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A359" s="8"/>
       <c r="B359" s="8"/>
       <c r="C359" s="8"/>
@@ -24534,10 +23877,8 @@
       <c r="AR359" s="8"/>
       <c r="AS359" s="8"/>
       <c r="AT359" s="8"/>
-      <c r="AU359" s="8"/>
-      <c r="AV359" s="8"/>
-    </row>
-    <row r="360" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A360" s="8"/>
       <c r="B360" s="8"/>
       <c r="C360" s="8"/>
@@ -24584,10 +23925,8 @@
       <c r="AR360" s="8"/>
       <c r="AS360" s="8"/>
       <c r="AT360" s="8"/>
-      <c r="AU360" s="8"/>
-      <c r="AV360" s="8"/>
-    </row>
-    <row r="361" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A361" s="8"/>
       <c r="B361" s="8"/>
       <c r="C361" s="8"/>
@@ -24634,10 +23973,8 @@
       <c r="AR361" s="8"/>
       <c r="AS361" s="8"/>
       <c r="AT361" s="8"/>
-      <c r="AU361" s="8"/>
-      <c r="AV361" s="8"/>
-    </row>
-    <row r="362" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A362" s="8"/>
       <c r="B362" s="8"/>
       <c r="C362" s="8"/>
@@ -24684,10 +24021,8 @@
       <c r="AR362" s="8"/>
       <c r="AS362" s="8"/>
       <c r="AT362" s="8"/>
-      <c r="AU362" s="8"/>
-      <c r="AV362" s="8"/>
-    </row>
-    <row r="363" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A363" s="8"/>
       <c r="B363" s="8"/>
       <c r="C363" s="8"/>
@@ -24734,10 +24069,8 @@
       <c r="AR363" s="8"/>
       <c r="AS363" s="8"/>
       <c r="AT363" s="8"/>
-      <c r="AU363" s="8"/>
-      <c r="AV363" s="8"/>
-    </row>
-    <row r="364" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A364" s="8"/>
       <c r="B364" s="8"/>
       <c r="C364" s="8"/>
@@ -24784,10 +24117,8 @@
       <c r="AR364" s="8"/>
       <c r="AS364" s="8"/>
       <c r="AT364" s="8"/>
-      <c r="AU364" s="8"/>
-      <c r="AV364" s="8"/>
-    </row>
-    <row r="365" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A365" s="8"/>
       <c r="B365" s="8"/>
       <c r="C365" s="8"/>
@@ -24834,10 +24165,8 @@
       <c r="AR365" s="8"/>
       <c r="AS365" s="8"/>
       <c r="AT365" s="8"/>
-      <c r="AU365" s="8"/>
-      <c r="AV365" s="8"/>
-    </row>
-    <row r="366" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A366" s="8"/>
       <c r="B366" s="8"/>
       <c r="C366" s="8"/>
@@ -24884,10 +24213,8 @@
       <c r="AR366" s="8"/>
       <c r="AS366" s="8"/>
       <c r="AT366" s="8"/>
-      <c r="AU366" s="8"/>
-      <c r="AV366" s="8"/>
-    </row>
-    <row r="367" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A367" s="8"/>
       <c r="B367" s="8"/>
       <c r="C367" s="8"/>
@@ -24934,10 +24261,8 @@
       <c r="AR367" s="8"/>
       <c r="AS367" s="8"/>
       <c r="AT367" s="8"/>
-      <c r="AU367" s="8"/>
-      <c r="AV367" s="8"/>
-    </row>
-    <row r="368" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A368" s="8"/>
       <c r="B368" s="8"/>
       <c r="C368" s="8"/>
@@ -24984,10 +24309,8 @@
       <c r="AR368" s="8"/>
       <c r="AS368" s="8"/>
       <c r="AT368" s="8"/>
-      <c r="AU368" s="8"/>
-      <c r="AV368" s="8"/>
-    </row>
-    <row r="369" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A369" s="8"/>
       <c r="B369" s="8"/>
       <c r="C369" s="8"/>
@@ -25034,10 +24357,8 @@
       <c r="AR369" s="8"/>
       <c r="AS369" s="8"/>
       <c r="AT369" s="8"/>
-      <c r="AU369" s="8"/>
-      <c r="AV369" s="8"/>
-    </row>
-    <row r="370" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A370" s="8"/>
       <c r="B370" s="8"/>
       <c r="C370" s="8"/>
@@ -25084,10 +24405,8 @@
       <c r="AR370" s="8"/>
       <c r="AS370" s="8"/>
       <c r="AT370" s="8"/>
-      <c r="AU370" s="8"/>
-      <c r="AV370" s="8"/>
-    </row>
-    <row r="371" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A371" s="8"/>
       <c r="B371" s="8"/>
       <c r="C371" s="8"/>
@@ -25134,10 +24453,8 @@
       <c r="AR371" s="8"/>
       <c r="AS371" s="8"/>
       <c r="AT371" s="8"/>
-      <c r="AU371" s="8"/>
-      <c r="AV371" s="8"/>
-    </row>
-    <row r="372" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A372" s="8"/>
       <c r="B372" s="8"/>
       <c r="C372" s="8"/>
@@ -25184,10 +24501,8 @@
       <c r="AR372" s="8"/>
       <c r="AS372" s="8"/>
       <c r="AT372" s="8"/>
-      <c r="AU372" s="8"/>
-      <c r="AV372" s="8"/>
-    </row>
-    <row r="373" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A373" s="8"/>
       <c r="B373" s="8"/>
       <c r="C373" s="8"/>
@@ -25234,10 +24549,8 @@
       <c r="AR373" s="8"/>
       <c r="AS373" s="8"/>
       <c r="AT373" s="8"/>
-      <c r="AU373" s="8"/>
-      <c r="AV373" s="8"/>
-    </row>
-    <row r="374" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A374" s="8"/>
       <c r="B374" s="8"/>
       <c r="C374" s="8"/>
@@ -25284,10 +24597,8 @@
       <c r="AR374" s="8"/>
       <c r="AS374" s="8"/>
       <c r="AT374" s="8"/>
-      <c r="AU374" s="8"/>
-      <c r="AV374" s="8"/>
-    </row>
-    <row r="375" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A375" s="8"/>
       <c r="B375" s="8"/>
       <c r="C375" s="8"/>
@@ -25334,10 +24645,8 @@
       <c r="AR375" s="8"/>
       <c r="AS375" s="8"/>
       <c r="AT375" s="8"/>
-      <c r="AU375" s="8"/>
-      <c r="AV375" s="8"/>
-    </row>
-    <row r="376" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A376" s="8"/>
       <c r="B376" s="8"/>
       <c r="C376" s="8"/>
@@ -25384,10 +24693,8 @@
       <c r="AR376" s="8"/>
       <c r="AS376" s="8"/>
       <c r="AT376" s="8"/>
-      <c r="AU376" s="8"/>
-      <c r="AV376" s="8"/>
-    </row>
-    <row r="377" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A377" s="8"/>
       <c r="B377" s="8"/>
       <c r="C377" s="8"/>
@@ -25434,10 +24741,8 @@
       <c r="AR377" s="8"/>
       <c r="AS377" s="8"/>
       <c r="AT377" s="8"/>
-      <c r="AU377" s="8"/>
-      <c r="AV377" s="8"/>
-    </row>
-    <row r="378" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A378" s="8"/>
       <c r="B378" s="8"/>
       <c r="C378" s="8"/>
@@ -25484,10 +24789,8 @@
       <c r="AR378" s="8"/>
       <c r="AS378" s="8"/>
       <c r="AT378" s="8"/>
-      <c r="AU378" s="8"/>
-      <c r="AV378" s="8"/>
-    </row>
-    <row r="379" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A379" s="8"/>
       <c r="B379" s="8"/>
       <c r="C379" s="8"/>
@@ -25534,10 +24837,8 @@
       <c r="AR379" s="8"/>
       <c r="AS379" s="8"/>
       <c r="AT379" s="8"/>
-      <c r="AU379" s="8"/>
-      <c r="AV379" s="8"/>
-    </row>
-    <row r="380" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A380" s="8"/>
       <c r="B380" s="8"/>
       <c r="C380" s="8"/>
@@ -25584,10 +24885,8 @@
       <c r="AR380" s="8"/>
       <c r="AS380" s="8"/>
       <c r="AT380" s="8"/>
-      <c r="AU380" s="8"/>
-      <c r="AV380" s="8"/>
-    </row>
-    <row r="381" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A381" s="8"/>
       <c r="B381" s="8"/>
       <c r="C381" s="8"/>
@@ -25634,10 +24933,8 @@
       <c r="AR381" s="8"/>
       <c r="AS381" s="8"/>
       <c r="AT381" s="8"/>
-      <c r="AU381" s="8"/>
-      <c r="AV381" s="8"/>
-    </row>
-    <row r="382" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A382" s="8"/>
       <c r="B382" s="8"/>
       <c r="C382" s="8"/>
@@ -25684,10 +24981,8 @@
       <c r="AR382" s="8"/>
       <c r="AS382" s="8"/>
       <c r="AT382" s="8"/>
-      <c r="AU382" s="8"/>
-      <c r="AV382" s="8"/>
-    </row>
-    <row r="383" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A383" s="8"/>
       <c r="B383" s="8"/>
       <c r="C383" s="8"/>
@@ -25734,10 +25029,8 @@
       <c r="AR383" s="8"/>
       <c r="AS383" s="8"/>
       <c r="AT383" s="8"/>
-      <c r="AU383" s="8"/>
-      <c r="AV383" s="8"/>
-    </row>
-    <row r="384" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A384" s="8"/>
       <c r="B384" s="8"/>
       <c r="C384" s="8"/>
@@ -25784,10 +25077,8 @@
       <c r="AR384" s="8"/>
       <c r="AS384" s="8"/>
       <c r="AT384" s="8"/>
-      <c r="AU384" s="8"/>
-      <c r="AV384" s="8"/>
-    </row>
-    <row r="385" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A385" s="8"/>
       <c r="B385" s="8"/>
       <c r="C385" s="8"/>
@@ -25834,10 +25125,8 @@
       <c r="AR385" s="8"/>
       <c r="AS385" s="8"/>
       <c r="AT385" s="8"/>
-      <c r="AU385" s="8"/>
-      <c r="AV385" s="8"/>
-    </row>
-    <row r="386" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A386" s="8"/>
       <c r="B386" s="8"/>
       <c r="C386" s="8"/>
@@ -25884,10 +25173,8 @@
       <c r="AR386" s="8"/>
       <c r="AS386" s="8"/>
       <c r="AT386" s="8"/>
-      <c r="AU386" s="8"/>
-      <c r="AV386" s="8"/>
-    </row>
-    <row r="387" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A387" s="8"/>
       <c r="B387" s="8"/>
       <c r="C387" s="8"/>
@@ -25934,10 +25221,8 @@
       <c r="AR387" s="8"/>
       <c r="AS387" s="8"/>
       <c r="AT387" s="8"/>
-      <c r="AU387" s="8"/>
-      <c r="AV387" s="8"/>
-    </row>
-    <row r="388" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A388" s="8"/>
       <c r="B388" s="8"/>
       <c r="C388" s="8"/>
@@ -25984,10 +25269,8 @@
       <c r="AR388" s="8"/>
       <c r="AS388" s="8"/>
       <c r="AT388" s="8"/>
-      <c r="AU388" s="8"/>
-      <c r="AV388" s="8"/>
-    </row>
-    <row r="389" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A389" s="8"/>
       <c r="B389" s="8"/>
       <c r="C389" s="8"/>
@@ -26034,10 +25317,8 @@
       <c r="AR389" s="8"/>
       <c r="AS389" s="8"/>
       <c r="AT389" s="8"/>
-      <c r="AU389" s="8"/>
-      <c r="AV389" s="8"/>
-    </row>
-    <row r="390" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A390" s="8"/>
       <c r="B390" s="8"/>
       <c r="C390" s="8"/>
@@ -26084,10 +25365,8 @@
       <c r="AR390" s="8"/>
       <c r="AS390" s="8"/>
       <c r="AT390" s="8"/>
-      <c r="AU390" s="8"/>
-      <c r="AV390" s="8"/>
-    </row>
-    <row r="391" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A391" s="8"/>
       <c r="B391" s="8"/>
       <c r="C391" s="8"/>
@@ -26134,10 +25413,8 @@
       <c r="AR391" s="8"/>
       <c r="AS391" s="8"/>
       <c r="AT391" s="8"/>
-      <c r="AU391" s="8"/>
-      <c r="AV391" s="8"/>
-    </row>
-    <row r="392" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A392" s="8"/>
       <c r="B392" s="8"/>
       <c r="C392" s="8"/>
@@ -26184,10 +25461,8 @@
       <c r="AR392" s="8"/>
       <c r="AS392" s="8"/>
       <c r="AT392" s="8"/>
-      <c r="AU392" s="8"/>
-      <c r="AV392" s="8"/>
-    </row>
-    <row r="393" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A393" s="8"/>
       <c r="B393" s="8"/>
       <c r="C393" s="8"/>
@@ -26234,10 +25509,8 @@
       <c r="AR393" s="8"/>
       <c r="AS393" s="8"/>
       <c r="AT393" s="8"/>
-      <c r="AU393" s="8"/>
-      <c r="AV393" s="8"/>
-    </row>
-    <row r="394" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A394" s="8"/>
       <c r="B394" s="8"/>
       <c r="C394" s="8"/>
@@ -26284,10 +25557,8 @@
       <c r="AR394" s="8"/>
       <c r="AS394" s="8"/>
       <c r="AT394" s="8"/>
-      <c r="AU394" s="8"/>
-      <c r="AV394" s="8"/>
-    </row>
-    <row r="395" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A395" s="8"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
@@ -26334,10 +25605,8 @@
       <c r="AR395" s="8"/>
       <c r="AS395" s="8"/>
       <c r="AT395" s="8"/>
-      <c r="AU395" s="8"/>
-      <c r="AV395" s="8"/>
-    </row>
-    <row r="396" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A396" s="8"/>
       <c r="B396" s="8"/>
       <c r="C396" s="8"/>
@@ -26384,10 +25653,8 @@
       <c r="AR396" s="8"/>
       <c r="AS396" s="8"/>
       <c r="AT396" s="8"/>
-      <c r="AU396" s="8"/>
-      <c r="AV396" s="8"/>
-    </row>
-    <row r="397" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A397" s="8"/>
       <c r="B397" s="8"/>
       <c r="C397" s="8"/>
@@ -26434,10 +25701,8 @@
       <c r="AR397" s="8"/>
       <c r="AS397" s="8"/>
       <c r="AT397" s="8"/>
-      <c r="AU397" s="8"/>
-      <c r="AV397" s="8"/>
-    </row>
-    <row r="398" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A398" s="8"/>
       <c r="B398" s="8"/>
       <c r="C398" s="8"/>
@@ -26484,10 +25749,8 @@
       <c r="AR398" s="8"/>
       <c r="AS398" s="8"/>
       <c r="AT398" s="8"/>
-      <c r="AU398" s="8"/>
-      <c r="AV398" s="8"/>
-    </row>
-    <row r="399" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A399" s="8"/>
       <c r="B399" s="8"/>
       <c r="C399" s="8"/>
@@ -26534,10 +25797,8 @@
       <c r="AR399" s="8"/>
       <c r="AS399" s="8"/>
       <c r="AT399" s="8"/>
-      <c r="AU399" s="8"/>
-      <c r="AV399" s="8"/>
-    </row>
-    <row r="400" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A400" s="8"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8"/>
@@ -26584,10 +25845,8 @@
       <c r="AR400" s="8"/>
       <c r="AS400" s="8"/>
       <c r="AT400" s="8"/>
-      <c r="AU400" s="8"/>
-      <c r="AV400" s="8"/>
-    </row>
-    <row r="401" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A401" s="8"/>
       <c r="B401" s="8"/>
       <c r="C401" s="8"/>
@@ -26634,10 +25893,8 @@
       <c r="AR401" s="8"/>
       <c r="AS401" s="8"/>
       <c r="AT401" s="8"/>
-      <c r="AU401" s="8"/>
-      <c r="AV401" s="8"/>
-    </row>
-    <row r="402" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A402" s="8"/>
       <c r="B402" s="8"/>
       <c r="C402" s="8"/>
@@ -26684,10 +25941,8 @@
       <c r="AR402" s="8"/>
       <c r="AS402" s="8"/>
       <c r="AT402" s="8"/>
-      <c r="AU402" s="8"/>
-      <c r="AV402" s="8"/>
-    </row>
-    <row r="403" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A403" s="8"/>
       <c r="B403" s="8"/>
       <c r="C403" s="8"/>
@@ -26734,10 +25989,8 @@
       <c r="AR403" s="8"/>
       <c r="AS403" s="8"/>
       <c r="AT403" s="8"/>
-      <c r="AU403" s="8"/>
-      <c r="AV403" s="8"/>
-    </row>
-    <row r="404" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A404" s="8"/>
       <c r="B404" s="8"/>
       <c r="C404" s="8"/>
@@ -26784,10 +26037,8 @@
       <c r="AR404" s="8"/>
       <c r="AS404" s="8"/>
       <c r="AT404" s="8"/>
-      <c r="AU404" s="8"/>
-      <c r="AV404" s="8"/>
-    </row>
-    <row r="405" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A405" s="8"/>
       <c r="B405" s="8"/>
       <c r="C405" s="8"/>
@@ -26834,10 +26085,8 @@
       <c r="AR405" s="8"/>
       <c r="AS405" s="8"/>
       <c r="AT405" s="8"/>
-      <c r="AU405" s="8"/>
-      <c r="AV405" s="8"/>
-    </row>
-    <row r="406" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A406" s="8"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
@@ -26884,10 +26133,8 @@
       <c r="AR406" s="8"/>
       <c r="AS406" s="8"/>
       <c r="AT406" s="8"/>
-      <c r="AU406" s="8"/>
-      <c r="AV406" s="8"/>
-    </row>
-    <row r="407" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A407" s="8"/>
       <c r="B407" s="8"/>
       <c r="C407" s="8"/>
@@ -26934,10 +26181,8 @@
       <c r="AR407" s="8"/>
       <c r="AS407" s="8"/>
       <c r="AT407" s="8"/>
-      <c r="AU407" s="8"/>
-      <c r="AV407" s="8"/>
-    </row>
-    <row r="408" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="408" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A408" s="8"/>
       <c r="B408" s="8"/>
       <c r="C408" s="8"/>
@@ -26984,10 +26229,8 @@
       <c r="AR408" s="8"/>
       <c r="AS408" s="8"/>
       <c r="AT408" s="8"/>
-      <c r="AU408" s="8"/>
-      <c r="AV408" s="8"/>
-    </row>
-    <row r="409" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A409" s="8"/>
       <c r="B409" s="8"/>
       <c r="C409" s="8"/>
@@ -27034,10 +26277,8 @@
       <c r="AR409" s="8"/>
       <c r="AS409" s="8"/>
       <c r="AT409" s="8"/>
-      <c r="AU409" s="8"/>
-      <c r="AV409" s="8"/>
-    </row>
-    <row r="410" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A410" s="8"/>
       <c r="B410" s="8"/>
       <c r="C410" s="8"/>
@@ -27084,10 +26325,8 @@
       <c r="AR410" s="8"/>
       <c r="AS410" s="8"/>
       <c r="AT410" s="8"/>
-      <c r="AU410" s="8"/>
-      <c r="AV410" s="8"/>
-    </row>
-    <row r="411" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A411" s="8"/>
       <c r="B411" s="8"/>
       <c r="C411" s="8"/>
@@ -27134,10 +26373,8 @@
       <c r="AR411" s="8"/>
       <c r="AS411" s="8"/>
       <c r="AT411" s="8"/>
-      <c r="AU411" s="8"/>
-      <c r="AV411" s="8"/>
-    </row>
-    <row r="412" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A412" s="8"/>
       <c r="B412" s="8"/>
       <c r="C412" s="8"/>
@@ -27184,10 +26421,8 @@
       <c r="AR412" s="8"/>
       <c r="AS412" s="8"/>
       <c r="AT412" s="8"/>
-      <c r="AU412" s="8"/>
-      <c r="AV412" s="8"/>
-    </row>
-    <row r="413" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A413" s="8"/>
       <c r="B413" s="8"/>
       <c r="C413" s="8"/>
@@ -27234,10 +26469,8 @@
       <c r="AR413" s="8"/>
       <c r="AS413" s="8"/>
       <c r="AT413" s="8"/>
-      <c r="AU413" s="8"/>
-      <c r="AV413" s="8"/>
-    </row>
-    <row r="414" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="414" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A414" s="8"/>
       <c r="B414" s="8"/>
       <c r="C414" s="8"/>
@@ -27284,10 +26517,8 @@
       <c r="AR414" s="8"/>
       <c r="AS414" s="8"/>
       <c r="AT414" s="8"/>
-      <c r="AU414" s="8"/>
-      <c r="AV414" s="8"/>
-    </row>
-    <row r="415" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="415" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A415" s="8"/>
       <c r="B415" s="8"/>
       <c r="C415" s="8"/>
@@ -27334,10 +26565,8 @@
       <c r="AR415" s="8"/>
       <c r="AS415" s="8"/>
       <c r="AT415" s="8"/>
-      <c r="AU415" s="8"/>
-      <c r="AV415" s="8"/>
-    </row>
-    <row r="416" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="416" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A416" s="8"/>
       <c r="B416" s="8"/>
       <c r="C416" s="8"/>
@@ -27384,10 +26613,8 @@
       <c r="AR416" s="8"/>
       <c r="AS416" s="8"/>
       <c r="AT416" s="8"/>
-      <c r="AU416" s="8"/>
-      <c r="AV416" s="8"/>
-    </row>
-    <row r="417" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="417" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A417" s="8"/>
       <c r="B417" s="8"/>
       <c r="C417" s="8"/>
@@ -27434,10 +26661,8 @@
       <c r="AR417" s="8"/>
       <c r="AS417" s="8"/>
       <c r="AT417" s="8"/>
-      <c r="AU417" s="8"/>
-      <c r="AV417" s="8"/>
-    </row>
-    <row r="418" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="418" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A418" s="8"/>
       <c r="B418" s="8"/>
       <c r="C418" s="8"/>
@@ -27484,10 +26709,8 @@
       <c r="AR418" s="8"/>
       <c r="AS418" s="8"/>
       <c r="AT418" s="8"/>
-      <c r="AU418" s="8"/>
-      <c r="AV418" s="8"/>
-    </row>
-    <row r="419" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A419" s="8"/>
       <c r="B419" s="8"/>
       <c r="C419" s="8"/>
@@ -27534,10 +26757,8 @@
       <c r="AR419" s="8"/>
       <c r="AS419" s="8"/>
       <c r="AT419" s="8"/>
-      <c r="AU419" s="8"/>
-      <c r="AV419" s="8"/>
-    </row>
-    <row r="420" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A420" s="8"/>
       <c r="B420" s="8"/>
       <c r="C420" s="8"/>
@@ -27584,10 +26805,8 @@
       <c r="AR420" s="8"/>
       <c r="AS420" s="8"/>
       <c r="AT420" s="8"/>
-      <c r="AU420" s="8"/>
-      <c r="AV420" s="8"/>
-    </row>
-    <row r="421" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="421" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A421" s="8"/>
       <c r="B421" s="8"/>
       <c r="C421" s="8"/>
@@ -27634,10 +26853,8 @@
       <c r="AR421" s="8"/>
       <c r="AS421" s="8"/>
       <c r="AT421" s="8"/>
-      <c r="AU421" s="8"/>
-      <c r="AV421" s="8"/>
-    </row>
-    <row r="422" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="422" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A422" s="8"/>
       <c r="B422" s="8"/>
       <c r="C422" s="8"/>
@@ -27684,10 +26901,8 @@
       <c r="AR422" s="8"/>
       <c r="AS422" s="8"/>
       <c r="AT422" s="8"/>
-      <c r="AU422" s="8"/>
-      <c r="AV422" s="8"/>
-    </row>
-    <row r="423" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A423" s="8"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8"/>
@@ -27734,10 +26949,8 @@
       <c r="AR423" s="8"/>
       <c r="AS423" s="8"/>
       <c r="AT423" s="8"/>
-      <c r="AU423" s="8"/>
-      <c r="AV423" s="8"/>
-    </row>
-    <row r="424" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A424" s="8"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8"/>
@@ -27784,10 +26997,8 @@
       <c r="AR424" s="8"/>
       <c r="AS424" s="8"/>
       <c r="AT424" s="8"/>
-      <c r="AU424" s="8"/>
-      <c r="AV424" s="8"/>
-    </row>
-    <row r="425" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A425" s="8"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8"/>
@@ -27834,10 +27045,8 @@
       <c r="AR425" s="8"/>
       <c r="AS425" s="8"/>
       <c r="AT425" s="8"/>
-      <c r="AU425" s="8"/>
-      <c r="AV425" s="8"/>
-    </row>
-    <row r="426" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A426" s="8"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8"/>
@@ -27884,10 +27093,8 @@
       <c r="AR426" s="8"/>
       <c r="AS426" s="8"/>
       <c r="AT426" s="8"/>
-      <c r="AU426" s="8"/>
-      <c r="AV426" s="8"/>
-    </row>
-    <row r="427" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A427" s="8"/>
       <c r="B427" s="8"/>
       <c r="C427" s="8"/>
@@ -27934,10 +27141,8 @@
       <c r="AR427" s="8"/>
       <c r="AS427" s="8"/>
       <c r="AT427" s="8"/>
-      <c r="AU427" s="8"/>
-      <c r="AV427" s="8"/>
-    </row>
-    <row r="428" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A428" s="8"/>
       <c r="B428" s="8"/>
       <c r="C428" s="8"/>
@@ -27984,10 +27189,8 @@
       <c r="AR428" s="8"/>
       <c r="AS428" s="8"/>
       <c r="AT428" s="8"/>
-      <c r="AU428" s="8"/>
-      <c r="AV428" s="8"/>
-    </row>
-    <row r="429" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="429" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A429" s="8"/>
       <c r="B429" s="8"/>
       <c r="C429" s="8"/>
@@ -28034,10 +27237,8 @@
       <c r="AR429" s="8"/>
       <c r="AS429" s="8"/>
       <c r="AT429" s="8"/>
-      <c r="AU429" s="8"/>
-      <c r="AV429" s="8"/>
-    </row>
-    <row r="430" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="430" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A430" s="8"/>
       <c r="B430" s="8"/>
       <c r="C430" s="8"/>
@@ -28084,10 +27285,8 @@
       <c r="AR430" s="8"/>
       <c r="AS430" s="8"/>
       <c r="AT430" s="8"/>
-      <c r="AU430" s="8"/>
-      <c r="AV430" s="8"/>
-    </row>
-    <row r="431" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="431" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
@@ -28134,10 +27333,8 @@
       <c r="AR431" s="8"/>
       <c r="AS431" s="8"/>
       <c r="AT431" s="8"/>
-      <c r="AU431" s="8"/>
-      <c r="AV431" s="8"/>
-    </row>
-    <row r="432" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="432" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A432" s="8"/>
       <c r="B432" s="8"/>
       <c r="C432" s="8"/>
@@ -28184,10 +27381,8 @@
       <c r="AR432" s="8"/>
       <c r="AS432" s="8"/>
       <c r="AT432" s="8"/>
-      <c r="AU432" s="8"/>
-      <c r="AV432" s="8"/>
-    </row>
-    <row r="433" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A433" s="8"/>
       <c r="B433" s="8"/>
       <c r="C433" s="8"/>
@@ -28234,10 +27429,8 @@
       <c r="AR433" s="8"/>
       <c r="AS433" s="8"/>
       <c r="AT433" s="8"/>
-      <c r="AU433" s="8"/>
-      <c r="AV433" s="8"/>
-    </row>
-    <row r="434" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A434" s="8"/>
       <c r="B434" s="8"/>
       <c r="C434" s="8"/>
@@ -28284,10 +27477,8 @@
       <c r="AR434" s="8"/>
       <c r="AS434" s="8"/>
       <c r="AT434" s="8"/>
-      <c r="AU434" s="8"/>
-      <c r="AV434" s="8"/>
-    </row>
-    <row r="435" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A435" s="8"/>
       <c r="B435" s="8"/>
       <c r="C435" s="8"/>
@@ -28334,10 +27525,8 @@
       <c r="AR435" s="8"/>
       <c r="AS435" s="8"/>
       <c r="AT435" s="8"/>
-      <c r="AU435" s="8"/>
-      <c r="AV435" s="8"/>
-    </row>
-    <row r="436" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A436" s="8"/>
       <c r="B436" s="8"/>
       <c r="C436" s="8"/>
@@ -28384,10 +27573,8 @@
       <c r="AR436" s="8"/>
       <c r="AS436" s="8"/>
       <c r="AT436" s="8"/>
-      <c r="AU436" s="8"/>
-      <c r="AV436" s="8"/>
-    </row>
-    <row r="437" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="437" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A437" s="8"/>
       <c r="B437" s="8"/>
       <c r="C437" s="8"/>
@@ -28434,10 +27621,8 @@
       <c r="AR437" s="8"/>
       <c r="AS437" s="8"/>
       <c r="AT437" s="8"/>
-      <c r="AU437" s="8"/>
-      <c r="AV437" s="8"/>
-    </row>
-    <row r="438" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="438" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A438" s="8"/>
       <c r="B438" s="8"/>
       <c r="C438" s="8"/>
@@ -28484,10 +27669,8 @@
       <c r="AR438" s="8"/>
       <c r="AS438" s="8"/>
       <c r="AT438" s="8"/>
-      <c r="AU438" s="8"/>
-      <c r="AV438" s="8"/>
-    </row>
-    <row r="439" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="439" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A439" s="8"/>
       <c r="B439" s="8"/>
       <c r="C439" s="8"/>
@@ -28534,10 +27717,8 @@
       <c r="AR439" s="8"/>
       <c r="AS439" s="8"/>
       <c r="AT439" s="8"/>
-      <c r="AU439" s="8"/>
-      <c r="AV439" s="8"/>
-    </row>
-    <row r="440" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="440" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A440" s="8"/>
       <c r="B440" s="8"/>
       <c r="C440" s="8"/>
@@ -28584,10 +27765,8 @@
       <c r="AR440" s="8"/>
       <c r="AS440" s="8"/>
       <c r="AT440" s="8"/>
-      <c r="AU440" s="8"/>
-      <c r="AV440" s="8"/>
-    </row>
-    <row r="441" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="441" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A441" s="8"/>
       <c r="B441" s="8"/>
       <c r="C441" s="8"/>
@@ -28634,10 +27813,8 @@
       <c r="AR441" s="8"/>
       <c r="AS441" s="8"/>
       <c r="AT441" s="8"/>
-      <c r="AU441" s="8"/>
-      <c r="AV441" s="8"/>
-    </row>
-    <row r="442" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="442" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
@@ -28684,10 +27861,8 @@
       <c r="AR442" s="8"/>
       <c r="AS442" s="8"/>
       <c r="AT442" s="8"/>
-      <c r="AU442" s="8"/>
-      <c r="AV442" s="8"/>
-    </row>
-    <row r="443" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="443" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A443" s="8"/>
       <c r="B443" s="8"/>
       <c r="C443" s="8"/>
@@ -28734,10 +27909,8 @@
       <c r="AR443" s="8"/>
       <c r="AS443" s="8"/>
       <c r="AT443" s="8"/>
-      <c r="AU443" s="8"/>
-      <c r="AV443" s="8"/>
-    </row>
-    <row r="444" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A444" s="8"/>
       <c r="B444" s="8"/>
       <c r="C444" s="8"/>
@@ -28784,10 +27957,8 @@
       <c r="AR444" s="8"/>
       <c r="AS444" s="8"/>
       <c r="AT444" s="8"/>
-      <c r="AU444" s="8"/>
-      <c r="AV444" s="8"/>
-    </row>
-    <row r="445" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A445" s="8"/>
       <c r="B445" s="8"/>
       <c r="C445" s="8"/>
@@ -28834,10 +28005,8 @@
       <c r="AR445" s="8"/>
       <c r="AS445" s="8"/>
       <c r="AT445" s="8"/>
-      <c r="AU445" s="8"/>
-      <c r="AV445" s="8"/>
-    </row>
-    <row r="446" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A446" s="8"/>
       <c r="B446" s="8"/>
       <c r="C446" s="8"/>
@@ -28884,10 +28053,8 @@
       <c r="AR446" s="8"/>
       <c r="AS446" s="8"/>
       <c r="AT446" s="8"/>
-      <c r="AU446" s="8"/>
-      <c r="AV446" s="8"/>
-    </row>
-    <row r="447" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A447" s="8"/>
       <c r="B447" s="8"/>
       <c r="C447" s="8"/>
@@ -28934,10 +28101,8 @@
       <c r="AR447" s="8"/>
       <c r="AS447" s="8"/>
       <c r="AT447" s="8"/>
-      <c r="AU447" s="8"/>
-      <c r="AV447" s="8"/>
-    </row>
-    <row r="448" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A448" s="8"/>
       <c r="B448" s="8"/>
       <c r="C448" s="8"/>
@@ -28984,10 +28149,8 @@
       <c r="AR448" s="8"/>
       <c r="AS448" s="8"/>
       <c r="AT448" s="8"/>
-      <c r="AU448" s="8"/>
-      <c r="AV448" s="8"/>
-    </row>
-    <row r="449" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A449" s="8"/>
       <c r="B449" s="8"/>
       <c r="C449" s="8"/>
@@ -29034,10 +28197,8 @@
       <c r="AR449" s="8"/>
       <c r="AS449" s="8"/>
       <c r="AT449" s="8"/>
-      <c r="AU449" s="8"/>
-      <c r="AV449" s="8"/>
-    </row>
-    <row r="450" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A450" s="8"/>
       <c r="B450" s="8"/>
       <c r="C450" s="8"/>
@@ -29084,10 +28245,8 @@
       <c r="AR450" s="8"/>
       <c r="AS450" s="8"/>
       <c r="AT450" s="8"/>
-      <c r="AU450" s="8"/>
-      <c r="AV450" s="8"/>
-    </row>
-    <row r="451" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="451" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
@@ -29134,10 +28293,8 @@
       <c r="AR451" s="8"/>
       <c r="AS451" s="8"/>
       <c r="AT451" s="8"/>
-      <c r="AU451" s="8"/>
-      <c r="AV451" s="8"/>
-    </row>
-    <row r="452" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="452" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A452" s="8"/>
       <c r="B452" s="8"/>
       <c r="C452" s="8"/>
@@ -29184,10 +28341,8 @@
       <c r="AR452" s="8"/>
       <c r="AS452" s="8"/>
       <c r="AT452" s="8"/>
-      <c r="AU452" s="8"/>
-      <c r="AV452" s="8"/>
-    </row>
-    <row r="453" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="453" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A453" s="8"/>
       <c r="B453" s="8"/>
       <c r="C453" s="8"/>
@@ -29234,10 +28389,8 @@
       <c r="AR453" s="8"/>
       <c r="AS453" s="8"/>
       <c r="AT453" s="8"/>
-      <c r="AU453" s="8"/>
-      <c r="AV453" s="8"/>
-    </row>
-    <row r="454" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="454" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A454" s="8"/>
       <c r="B454" s="8"/>
       <c r="C454" s="8"/>
@@ -29284,10 +28437,8 @@
       <c r="AR454" s="8"/>
       <c r="AS454" s="8"/>
       <c r="AT454" s="8"/>
-      <c r="AU454" s="8"/>
-      <c r="AV454" s="8"/>
-    </row>
-    <row r="455" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="455" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A455" s="8"/>
       <c r="B455" s="8"/>
       <c r="C455" s="8"/>
@@ -29334,10 +28485,8 @@
       <c r="AR455" s="8"/>
       <c r="AS455" s="8"/>
       <c r="AT455" s="8"/>
-      <c r="AU455" s="8"/>
-      <c r="AV455" s="8"/>
-    </row>
-    <row r="456" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="456" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A456" s="8"/>
       <c r="B456" s="8"/>
       <c r="C456" s="8"/>
@@ -29384,10 +28533,8 @@
       <c r="AR456" s="8"/>
       <c r="AS456" s="8"/>
       <c r="AT456" s="8"/>
-      <c r="AU456" s="8"/>
-      <c r="AV456" s="8"/>
-    </row>
-    <row r="457" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="457" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A457" s="8"/>
       <c r="B457" s="8"/>
       <c r="C457" s="8"/>
@@ -29434,10 +28581,8 @@
       <c r="AR457" s="8"/>
       <c r="AS457" s="8"/>
       <c r="AT457" s="8"/>
-      <c r="AU457" s="8"/>
-      <c r="AV457" s="8"/>
-    </row>
-    <row r="458" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="458" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A458" s="8"/>
       <c r="B458" s="8"/>
       <c r="C458" s="8"/>
@@ -29484,10 +28629,8 @@
       <c r="AR458" s="8"/>
       <c r="AS458" s="8"/>
       <c r="AT458" s="8"/>
-      <c r="AU458" s="8"/>
-      <c r="AV458" s="8"/>
-    </row>
-    <row r="459" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="459" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A459" s="8"/>
       <c r="B459" s="8"/>
       <c r="C459" s="8"/>
@@ -29534,10 +28677,8 @@
       <c r="AR459" s="8"/>
       <c r="AS459" s="8"/>
       <c r="AT459" s="8"/>
-      <c r="AU459" s="8"/>
-      <c r="AV459" s="8"/>
-    </row>
-    <row r="460" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="460" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A460" s="8"/>
       <c r="B460" s="8"/>
       <c r="C460" s="8"/>
@@ -29584,10 +28725,8 @@
       <c r="AR460" s="8"/>
       <c r="AS460" s="8"/>
       <c r="AT460" s="8"/>
-      <c r="AU460" s="8"/>
-      <c r="AV460" s="8"/>
-    </row>
-    <row r="461" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="461" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A461" s="8"/>
       <c r="B461" s="8"/>
       <c r="C461" s="8"/>
@@ -29634,10 +28773,8 @@
       <c r="AR461" s="8"/>
       <c r="AS461" s="8"/>
       <c r="AT461" s="8"/>
-      <c r="AU461" s="8"/>
-      <c r="AV461" s="8"/>
-    </row>
-    <row r="462" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="462" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A462" s="8"/>
       <c r="B462" s="8"/>
       <c r="C462" s="8"/>
@@ -29684,10 +28821,8 @@
       <c r="AR462" s="8"/>
       <c r="AS462" s="8"/>
       <c r="AT462" s="8"/>
-      <c r="AU462" s="8"/>
-      <c r="AV462" s="8"/>
-    </row>
-    <row r="463" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A463" s="8"/>
       <c r="B463" s="8"/>
       <c r="C463" s="8"/>
@@ -29734,10 +28869,8 @@
       <c r="AR463" s="8"/>
       <c r="AS463" s="8"/>
       <c r="AT463" s="8"/>
-      <c r="AU463" s="8"/>
-      <c r="AV463" s="8"/>
-    </row>
-    <row r="464" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="464" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A464" s="8"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8"/>
@@ -29784,10 +28917,8 @@
       <c r="AR464" s="8"/>
       <c r="AS464" s="8"/>
       <c r="AT464" s="8"/>
-      <c r="AU464" s="8"/>
-      <c r="AV464" s="8"/>
-    </row>
-    <row r="465" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="465" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A465" s="8"/>
       <c r="B465" s="8"/>
       <c r="C465" s="8"/>
@@ -29834,10 +28965,8 @@
       <c r="AR465" s="8"/>
       <c r="AS465" s="8"/>
       <c r="AT465" s="8"/>
-      <c r="AU465" s="8"/>
-      <c r="AV465" s="8"/>
-    </row>
-    <row r="466" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="466" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8"/>
@@ -29884,10 +29013,8 @@
       <c r="AR466" s="8"/>
       <c r="AS466" s="8"/>
       <c r="AT466" s="8"/>
-      <c r="AU466" s="8"/>
-      <c r="AV466" s="8"/>
-    </row>
-    <row r="467" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="467" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8"/>
@@ -29934,10 +29061,8 @@
       <c r="AR467" s="8"/>
       <c r="AS467" s="8"/>
       <c r="AT467" s="8"/>
-      <c r="AU467" s="8"/>
-      <c r="AV467" s="8"/>
-    </row>
-    <row r="468" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="468" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8"/>
@@ -29984,10 +29109,8 @@
       <c r="AR468" s="8"/>
       <c r="AS468" s="8"/>
       <c r="AT468" s="8"/>
-      <c r="AU468" s="8"/>
-      <c r="AV468" s="8"/>
-    </row>
-    <row r="469" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="469" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8"/>
@@ -30034,10 +29157,8 @@
       <c r="AR469" s="8"/>
       <c r="AS469" s="8"/>
       <c r="AT469" s="8"/>
-      <c r="AU469" s="8"/>
-      <c r="AV469" s="8"/>
-    </row>
-    <row r="470" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="470" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
@@ -30084,10 +29205,8 @@
       <c r="AR470" s="8"/>
       <c r="AS470" s="8"/>
       <c r="AT470" s="8"/>
-      <c r="AU470" s="8"/>
-      <c r="AV470" s="8"/>
-    </row>
-    <row r="471" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A471" s="8"/>
       <c r="B471" s="8"/>
       <c r="C471" s="8"/>
@@ -30134,10 +29253,8 @@
       <c r="AR471" s="8"/>
       <c r="AS471" s="8"/>
       <c r="AT471" s="8"/>
-      <c r="AU471" s="8"/>
-      <c r="AV471" s="8"/>
-    </row>
-    <row r="472" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A472" s="8"/>
       <c r="B472" s="8"/>
       <c r="C472" s="8"/>
@@ -30184,10 +29301,8 @@
       <c r="AR472" s="8"/>
       <c r="AS472" s="8"/>
       <c r="AT472" s="8"/>
-      <c r="AU472" s="8"/>
-      <c r="AV472" s="8"/>
-    </row>
-    <row r="473" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="473" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A473" s="8"/>
       <c r="B473" s="8"/>
       <c r="C473" s="8"/>
@@ -30234,10 +29349,8 @@
       <c r="AR473" s="8"/>
       <c r="AS473" s="8"/>
       <c r="AT473" s="8"/>
-      <c r="AU473" s="8"/>
-      <c r="AV473" s="8"/>
-    </row>
-    <row r="474" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="474" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A474" s="8"/>
       <c r="B474" s="8"/>
       <c r="C474" s="8"/>
@@ -30284,10 +29397,8 @@
       <c r="AR474" s="8"/>
       <c r="AS474" s="8"/>
       <c r="AT474" s="8"/>
-      <c r="AU474" s="8"/>
-      <c r="AV474" s="8"/>
-    </row>
-    <row r="475" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="475" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A475" s="8"/>
       <c r="B475" s="8"/>
       <c r="C475" s="8"/>
@@ -30334,10 +29445,8 @@
       <c r="AR475" s="8"/>
       <c r="AS475" s="8"/>
       <c r="AT475" s="8"/>
-      <c r="AU475" s="8"/>
-      <c r="AV475" s="8"/>
-    </row>
-    <row r="476" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="476" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A476" s="8"/>
       <c r="B476" s="8"/>
       <c r="C476" s="8"/>
@@ -30384,10 +29493,8 @@
       <c r="AR476" s="8"/>
       <c r="AS476" s="8"/>
       <c r="AT476" s="8"/>
-      <c r="AU476" s="8"/>
-      <c r="AV476" s="8"/>
-    </row>
-    <row r="477" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="477" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A477" s="8"/>
       <c r="B477" s="8"/>
       <c r="C477" s="8"/>
@@ -30434,10 +29541,8 @@
       <c r="AR477" s="8"/>
       <c r="AS477" s="8"/>
       <c r="AT477" s="8"/>
-      <c r="AU477" s="8"/>
-      <c r="AV477" s="8"/>
-    </row>
-    <row r="478" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="478" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A478" s="8"/>
       <c r="B478" s="8"/>
       <c r="C478" s="8"/>
@@ -30484,10 +29589,8 @@
       <c r="AR478" s="8"/>
       <c r="AS478" s="8"/>
       <c r="AT478" s="8"/>
-      <c r="AU478" s="8"/>
-      <c r="AV478" s="8"/>
-    </row>
-    <row r="479" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="479" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A479" s="8"/>
       <c r="B479" s="8"/>
       <c r="C479" s="8"/>
@@ -30534,10 +29637,8 @@
       <c r="AR479" s="8"/>
       <c r="AS479" s="8"/>
       <c r="AT479" s="8"/>
-      <c r="AU479" s="8"/>
-      <c r="AV479" s="8"/>
-    </row>
-    <row r="480" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="480" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A480" s="8"/>
       <c r="B480" s="8"/>
       <c r="C480" s="8"/>
@@ -30584,10 +29685,8 @@
       <c r="AR480" s="8"/>
       <c r="AS480" s="8"/>
       <c r="AT480" s="8"/>
-      <c r="AU480" s="8"/>
-      <c r="AV480" s="8"/>
-    </row>
-    <row r="481" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A481" s="8"/>
       <c r="B481" s="8"/>
       <c r="C481" s="8"/>
@@ -30634,10 +29733,8 @@
       <c r="AR481" s="8"/>
       <c r="AS481" s="8"/>
       <c r="AT481" s="8"/>
-      <c r="AU481" s="8"/>
-      <c r="AV481" s="8"/>
-    </row>
-    <row r="482" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A482" s="8"/>
       <c r="B482" s="8"/>
       <c r="C482" s="8"/>
@@ -30684,10 +29781,8 @@
       <c r="AR482" s="8"/>
       <c r="AS482" s="8"/>
       <c r="AT482" s="8"/>
-      <c r="AU482" s="8"/>
-      <c r="AV482" s="8"/>
-    </row>
-    <row r="483" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A483" s="8"/>
       <c r="B483" s="8"/>
       <c r="C483" s="8"/>
@@ -30734,10 +29829,8 @@
       <c r="AR483" s="8"/>
       <c r="AS483" s="8"/>
       <c r="AT483" s="8"/>
-      <c r="AU483" s="8"/>
-      <c r="AV483" s="8"/>
-    </row>
-    <row r="484" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A484" s="8"/>
       <c r="B484" s="8"/>
       <c r="C484" s="8"/>
@@ -30784,10 +29877,8 @@
       <c r="AR484" s="8"/>
       <c r="AS484" s="8"/>
       <c r="AT484" s="8"/>
-      <c r="AU484" s="8"/>
-      <c r="AV484" s="8"/>
-    </row>
-    <row r="485" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A485" s="8"/>
       <c r="B485" s="8"/>
       <c r="C485" s="8"/>
@@ -30834,10 +29925,8 @@
       <c r="AR485" s="8"/>
       <c r="AS485" s="8"/>
       <c r="AT485" s="8"/>
-      <c r="AU485" s="8"/>
-      <c r="AV485" s="8"/>
-    </row>
-    <row r="486" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A486" s="8"/>
       <c r="B486" s="8"/>
       <c r="C486" s="8"/>
@@ -30884,10 +29973,8 @@
       <c r="AR486" s="8"/>
       <c r="AS486" s="8"/>
       <c r="AT486" s="8"/>
-      <c r="AU486" s="8"/>
-      <c r="AV486" s="8"/>
-    </row>
-    <row r="487" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A487" s="8"/>
       <c r="B487" s="8"/>
       <c r="C487" s="8"/>
@@ -30934,10 +30021,8 @@
       <c r="AR487" s="8"/>
       <c r="AS487" s="8"/>
       <c r="AT487" s="8"/>
-      <c r="AU487" s="8"/>
-      <c r="AV487" s="8"/>
-    </row>
-    <row r="488" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A488" s="8"/>
       <c r="B488" s="8"/>
       <c r="C488" s="8"/>
@@ -30984,10 +30069,8 @@
       <c r="AR488" s="8"/>
       <c r="AS488" s="8"/>
       <c r="AT488" s="8"/>
-      <c r="AU488" s="8"/>
-      <c r="AV488" s="8"/>
-    </row>
-    <row r="489" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A489" s="8"/>
       <c r="B489" s="8"/>
       <c r="C489" s="8"/>
@@ -31034,10 +30117,8 @@
       <c r="AR489" s="8"/>
       <c r="AS489" s="8"/>
       <c r="AT489" s="8"/>
-      <c r="AU489" s="8"/>
-      <c r="AV489" s="8"/>
-    </row>
-    <row r="490" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A490" s="8"/>
       <c r="B490" s="8"/>
       <c r="C490" s="8"/>
@@ -31084,10 +30165,8 @@
       <c r="AR490" s="8"/>
       <c r="AS490" s="8"/>
       <c r="AT490" s="8"/>
-      <c r="AU490" s="8"/>
-      <c r="AV490" s="8"/>
-    </row>
-    <row r="491" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A491" s="8"/>
       <c r="B491" s="8"/>
       <c r="C491" s="8"/>
@@ -31134,10 +30213,8 @@
       <c r="AR491" s="8"/>
       <c r="AS491" s="8"/>
       <c r="AT491" s="8"/>
-      <c r="AU491" s="8"/>
-      <c r="AV491" s="8"/>
-    </row>
-    <row r="492" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="492" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A492" s="8"/>
       <c r="B492" s="8"/>
       <c r="C492" s="8"/>
@@ -31184,10 +30261,8 @@
       <c r="AR492" s="8"/>
       <c r="AS492" s="8"/>
       <c r="AT492" s="8"/>
-      <c r="AU492" s="8"/>
-      <c r="AV492" s="8"/>
-    </row>
-    <row r="493" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="493" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A493" s="8"/>
       <c r="B493" s="8"/>
       <c r="C493" s="8"/>
@@ -31234,10 +30309,8 @@
       <c r="AR493" s="8"/>
       <c r="AS493" s="8"/>
       <c r="AT493" s="8"/>
-      <c r="AU493" s="8"/>
-      <c r="AV493" s="8"/>
-    </row>
-    <row r="494" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="494" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A494" s="8"/>
       <c r="B494" s="8"/>
       <c r="C494" s="8"/>
@@ -31284,10 +30357,8 @@
       <c r="AR494" s="8"/>
       <c r="AS494" s="8"/>
       <c r="AT494" s="8"/>
-      <c r="AU494" s="8"/>
-      <c r="AV494" s="8"/>
-    </row>
-    <row r="495" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="495" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A495" s="8"/>
       <c r="B495" s="8"/>
       <c r="C495" s="8"/>
@@ -31334,10 +30405,8 @@
       <c r="AR495" s="8"/>
       <c r="AS495" s="8"/>
       <c r="AT495" s="8"/>
-      <c r="AU495" s="8"/>
-      <c r="AV495" s="8"/>
-    </row>
-    <row r="496" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="496" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A496" s="8"/>
       <c r="B496" s="8"/>
       <c r="C496" s="8"/>
@@ -31384,10 +30453,8 @@
       <c r="AR496" s="8"/>
       <c r="AS496" s="8"/>
       <c r="AT496" s="8"/>
-      <c r="AU496" s="8"/>
-      <c r="AV496" s="8"/>
-    </row>
-    <row r="497" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A497" s="8"/>
       <c r="B497" s="8"/>
       <c r="C497" s="8"/>
@@ -31434,10 +30501,8 @@
       <c r="AR497" s="8"/>
       <c r="AS497" s="8"/>
       <c r="AT497" s="8"/>
-      <c r="AU497" s="8"/>
-      <c r="AV497" s="8"/>
-    </row>
-    <row r="498" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="498" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A498" s="8"/>
       <c r="B498" s="8"/>
       <c r="C498" s="8"/>
@@ -31484,33 +30549,9 @@
       <c r="AR498" s="8"/>
       <c r="AS498" s="8"/>
       <c r="AT498" s="8"/>
-      <c r="AU498" s="8"/>
-      <c r="AV498" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AB108" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters blank="1">
-        <filter val="0,09"/>
-        <filter val="0,10"/>
-        <filter val="0,12"/>
-        <filter val="0,15"/>
-        <filter val="0,18"/>
-        <filter val="0,22"/>
-        <filter val="0,25"/>
-        <filter val="0,28"/>
-        <filter val="0,30"/>
-        <filter val="0,33"/>
-        <filter val="0,35"/>
-        <filter val="0,36"/>
-        <filter val="0,40"/>
-        <filter val="0,41"/>
-        <filter val="0,60"/>
-        <filter val="0,62"/>
-        <filter val="1,00"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AB108" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
